--- a/pages/CNT Data.xlsx
+++ b/pages/CNT Data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="949">
   <si>
     <t>Width</t>
   </si>
@@ -2844,6 +2844,33 @@
   </si>
   <si>
     <t>Megamax, Ultimate Ceramic 70% 40"X 50'</t>
+  </si>
+  <si>
+    <t>B-PPF-PGCC6050 (PPF, Premium Guard Clear Color Cap 60"x50')</t>
+  </si>
+  <si>
+    <t>PPF-GCCC60</t>
+  </si>
+  <si>
+    <t>Ceramic Shield PPF - Gloss Clear Color Cap</t>
+  </si>
+  <si>
+    <t>(PPF, Premium Guard Clear Color Cap 60"x50')</t>
+  </si>
+  <si>
+    <t>Filmstar</t>
+  </si>
+  <si>
+    <t>(iCool Carbon, 30% 40" x 100')</t>
+  </si>
+  <si>
+    <t>(iCool Carbon, 30% 60" x 100')</t>
+  </si>
+  <si>
+    <t>(iCool Ceramic Premium IR, 30% 40" x 100')</t>
+  </si>
+  <si>
+    <t>(iCool Ceramic Premium IR, 30% 60" x 100')</t>
   </si>
 </sst>
 </file>
@@ -2915,7 +2942,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2949,6 +2976,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2989,7 +3022,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3031,6 +3064,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3342,7 +3381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S353"/>
+  <dimension ref="A1:U354"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" bestFit="1" customWidth="1"/>
@@ -3361,68 +3400,73 @@
     <col min="15" max="15" width="6.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="38.7109375" customWidth="1"/>
     <col min="17" max="17" width="7" customWidth="1"/>
-    <col min="18" max="18" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="38.7109375" customWidth="1"/>
+    <col min="20" max="20" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:21">
+      <c r="A1" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="23" t="s">
         <v>360</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="25" t="s">
         <v>348</v>
       </c>
-      <c r="K1" s="23"/>
-      <c r="L1" s="24" t="s">
+      <c r="K1" s="25"/>
+      <c r="L1" s="26" t="s">
         <v>349</v>
       </c>
-      <c r="M1" s="24"/>
-      <c r="N1" s="25" t="s">
+      <c r="M1" s="26"/>
+      <c r="N1" s="27" t="s">
         <v>855</v>
       </c>
-      <c r="O1" s="25"/>
-      <c r="P1" s="19" t="s">
+      <c r="O1" s="27"/>
+      <c r="P1" s="21" t="s">
         <v>350</v>
       </c>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="20" t="s">
+      <c r="Q1" s="21"/>
+      <c r="R1" s="22" t="s">
         <v>584</v>
       </c>
-      <c r="S1" s="20"/>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="20" t="s">
+        <v>944</v>
+      </c>
+      <c r="U1" s="20"/>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="24"/>
       <c r="J2" s="10" t="s">
         <v>351</v>
       </c>
@@ -3453,8 +3497,14 @@
       <c r="S2" s="13" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="T2" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="U2" s="19" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="1" t="s">
         <v>373</v>
       </c>
@@ -3492,7 +3542,7 @@
         <v>99.7</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:21">
       <c r="A4" s="1" t="s">
         <v>374</v>
       </c>
@@ -3530,7 +3580,7 @@
         <v>142.43</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:21">
       <c r="A5" s="1" t="s">
         <v>375</v>
       </c>
@@ -3568,7 +3618,7 @@
         <v>142.43</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:21">
       <c r="A6" s="1" t="s">
         <v>376</v>
       </c>
@@ -3601,7 +3651,7 @@
       </c>
       <c r="P6" s="2"/>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:21">
       <c r="A7" s="1" t="s">
         <v>376</v>
       </c>
@@ -3635,7 +3685,7 @@
       </c>
       <c r="P7" s="2"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:21">
       <c r="A8" s="1" t="s">
         <v>376</v>
       </c>
@@ -3677,7 +3727,7 @@
       </c>
       <c r="P8" s="2"/>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:21">
       <c r="A9" s="1" t="s">
         <v>376</v>
       </c>
@@ -3719,7 +3769,7 @@
       </c>
       <c r="P9" s="2"/>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:21">
       <c r="A10" s="1" t="s">
         <v>376</v>
       </c>
@@ -3761,7 +3811,7 @@
       </c>
       <c r="P10" s="2"/>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:21">
       <c r="A11" s="1" t="s">
         <v>376</v>
       </c>
@@ -3803,7 +3853,7 @@
       </c>
       <c r="P11" s="2"/>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:21">
       <c r="A12" s="1" t="s">
         <v>376</v>
       </c>
@@ -3845,7 +3895,7 @@
       </c>
       <c r="P12" s="2"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:21">
       <c r="A13" s="1" t="s">
         <v>376</v>
       </c>
@@ -3887,7 +3937,7 @@
       </c>
       <c r="P13" s="2"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:21">
       <c r="A14" s="1" t="s">
         <v>377</v>
       </c>
@@ -3932,7 +3982,7 @@
       </c>
       <c r="P14" s="2"/>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:21">
       <c r="A15" s="1" t="s">
         <v>378</v>
       </c>
@@ -3977,7 +4027,7 @@
       </c>
       <c r="P15" s="2"/>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:21">
       <c r="A16" s="1" t="s">
         <v>379</v>
       </c>
@@ -4028,8 +4078,14 @@
         <f>I16-3</f>
         <v>75</v>
       </c>
-    </row>
-    <row r="17" spans="1:19">
+      <c r="T16" t="s">
+        <v>585</v>
+      </c>
+      <c r="U16">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="1" t="s">
         <v>380</v>
       </c>
@@ -4069,8 +4125,14 @@
         <f>I17</f>
         <v>107</v>
       </c>
-    </row>
-    <row r="18" spans="1:19">
+      <c r="T17" t="s">
+        <v>586</v>
+      </c>
+      <c r="U17">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" s="1" t="s">
         <v>380</v>
       </c>
@@ -4110,7 +4172,7 @@
       </c>
       <c r="P18" s="2"/>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:21">
       <c r="A19" s="1" t="s">
         <v>380</v>
       </c>
@@ -4158,7 +4220,7 @@
       </c>
       <c r="P19" s="2"/>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:21">
       <c r="A20" s="1" t="s">
         <v>380</v>
       </c>
@@ -4206,7 +4268,7 @@
       </c>
       <c r="P20" s="2"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:21">
       <c r="A21" s="1" t="s">
         <v>380</v>
       </c>
@@ -4254,7 +4316,7 @@
       </c>
       <c r="P21" s="2"/>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:21">
       <c r="A22" s="1" t="s">
         <v>380</v>
       </c>
@@ -4302,7 +4364,7 @@
       </c>
       <c r="P22" s="2"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:21">
       <c r="A23" s="1" t="s">
         <v>380</v>
       </c>
@@ -4350,7 +4412,7 @@
       </c>
       <c r="P23" s="2"/>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:21">
       <c r="A24" s="1" t="s">
         <v>380</v>
       </c>
@@ -4398,7 +4460,7 @@
       </c>
       <c r="P24" s="2"/>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:21">
       <c r="A25" s="1" t="s">
         <v>381</v>
       </c>
@@ -4443,7 +4505,7 @@
       </c>
       <c r="P25" s="2"/>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:21">
       <c r="A26" s="1" t="s">
         <v>382</v>
       </c>
@@ -4488,7 +4550,7 @@
       </c>
       <c r="P26" s="2"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:21">
       <c r="A27" s="1" t="s">
         <v>383</v>
       </c>
@@ -4539,8 +4601,14 @@
         <f>I27-3</f>
         <v>75</v>
       </c>
-    </row>
-    <row r="28" spans="1:19">
+      <c r="T27" t="s">
+        <v>587</v>
+      </c>
+      <c r="U27">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28" s="1" t="s">
         <v>384</v>
       </c>
@@ -4562,8 +4630,8 @@
       <c r="H28" s="3">
         <v>1.5</v>
       </c>
-      <c r="I28" s="18">
-        <v>103</v>
+      <c r="I28" s="2">
+        <v>107</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>64</v>
@@ -4578,10 +4646,16 @@
       </c>
       <c r="S28">
         <f>I28</f>
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19">
+        <v>107</v>
+      </c>
+      <c r="T28" t="s">
+        <v>588</v>
+      </c>
+      <c r="U28">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29" s="1" t="s">
         <v>384</v>
       </c>
@@ -4603,8 +4677,8 @@
       <c r="H29" s="3">
         <v>1.5</v>
       </c>
-      <c r="I29" s="18">
-        <v>107</v>
+      <c r="I29" s="2">
+        <v>111</v>
       </c>
       <c r="J29" s="5"/>
       <c r="L29" s="5" t="s">
@@ -4621,7 +4695,7 @@
       </c>
       <c r="P29" s="2"/>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:21">
       <c r="A30" s="1" t="s">
         <v>384</v>
       </c>
@@ -4646,8 +4720,8 @@
       <c r="H30" s="3">
         <v>1.5</v>
       </c>
-      <c r="I30" s="18">
-        <v>110</v>
+      <c r="I30" s="2">
+        <v>114</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>64</v>
@@ -4669,7 +4743,7 @@
       </c>
       <c r="P30" s="2"/>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:21">
       <c r="A31" s="1" t="s">
         <v>384</v>
       </c>
@@ -4694,8 +4768,8 @@
       <c r="H31" s="3">
         <v>1.5</v>
       </c>
-      <c r="I31" s="18">
-        <v>110</v>
+      <c r="I31" s="2">
+        <v>114</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>64</v>
@@ -4717,7 +4791,7 @@
       </c>
       <c r="P31" s="2"/>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:21">
       <c r="A32" s="1" t="s">
         <v>385</v>
       </c>
@@ -4740,7 +4814,7 @@
         <v>1.5</v>
       </c>
       <c r="I32" s="18">
-        <v>55</v>
+        <v>55.5</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>65</v>
@@ -4762,7 +4836,7 @@
       </c>
       <c r="P32" s="2"/>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:21">
       <c r="A33" s="1" t="s">
         <v>386</v>
       </c>
@@ -4807,7 +4881,7 @@
       </c>
       <c r="P33" s="2"/>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:21">
       <c r="A34" s="1" t="s">
         <v>387</v>
       </c>
@@ -4858,8 +4932,14 @@
         <f>I34-3</f>
         <v>75</v>
       </c>
-    </row>
-    <row r="35" spans="1:19">
+      <c r="T34" t="s">
+        <v>589</v>
+      </c>
+      <c r="U34">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35" s="1" t="s">
         <v>388</v>
       </c>
@@ -4899,8 +4979,14 @@
         <f>I35</f>
         <v>103</v>
       </c>
-    </row>
-    <row r="36" spans="1:19">
+      <c r="T35" t="s">
+        <v>590</v>
+      </c>
+      <c r="U35">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36" s="1" t="s">
         <v>388</v>
       </c>
@@ -4940,7 +5026,7 @@
       </c>
       <c r="P36" s="2"/>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:21">
       <c r="A37" s="1" t="s">
         <v>388</v>
       </c>
@@ -4988,7 +5074,7 @@
       </c>
       <c r="P37" s="2"/>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:21">
       <c r="A38" s="1" t="s">
         <v>388</v>
       </c>
@@ -5036,7 +5122,7 @@
       </c>
       <c r="P38" s="2"/>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:21">
       <c r="A39" s="1" t="s">
         <v>389</v>
       </c>
@@ -5081,7 +5167,7 @@
       </c>
       <c r="P39" s="2"/>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:21">
       <c r="A40" s="1" t="s">
         <v>390</v>
       </c>
@@ -5126,7 +5212,7 @@
       </c>
       <c r="P40" s="2"/>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:21">
       <c r="A41" s="1" t="s">
         <v>391</v>
       </c>
@@ -5169,8 +5255,14 @@
       <c r="O41" s="3">
         <v>130</v>
       </c>
-    </row>
-    <row r="42" spans="1:19">
+      <c r="R41" s="14" t="s">
+        <v>945</v>
+      </c>
+      <c r="S41">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42" s="1" t="s">
         <v>392</v>
       </c>
@@ -5202,8 +5294,14 @@
         <v>182.6</v>
       </c>
       <c r="N42"/>
-    </row>
-    <row r="43" spans="1:19">
+      <c r="R42" s="14" t="s">
+        <v>946</v>
+      </c>
+      <c r="S42">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43" s="1" t="s">
         <v>392</v>
       </c>
@@ -5242,7 +5340,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:21">
       <c r="A44" s="1" t="s">
         <v>392</v>
       </c>
@@ -5289,7 +5387,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:21">
       <c r="A45" s="1" t="s">
         <v>392</v>
       </c>
@@ -5336,7 +5434,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:21">
       <c r="A46" s="1" t="s">
         <v>393</v>
       </c>
@@ -5380,7 +5478,7 @@
         <v>96.25</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:21">
       <c r="A47" s="1" t="s">
         <v>394</v>
       </c>
@@ -5424,7 +5522,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:21">
       <c r="A48" s="1" t="s">
         <v>395</v>
       </c>
@@ -5473,8 +5571,14 @@
       <c r="S48">
         <v>75</v>
       </c>
-    </row>
-    <row r="49" spans="1:19">
+      <c r="T48" t="s">
+        <v>591</v>
+      </c>
+      <c r="U48">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49" s="1" t="s">
         <v>396</v>
       </c>
@@ -5512,8 +5616,14 @@
       <c r="S49">
         <v>103</v>
       </c>
-    </row>
-    <row r="50" spans="1:19">
+      <c r="T49" t="s">
+        <v>592</v>
+      </c>
+      <c r="U49">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
       <c r="A50" s="1" t="s">
         <v>396</v>
       </c>
@@ -5552,7 +5662,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:21">
       <c r="A51" s="1" t="s">
         <v>396</v>
       </c>
@@ -5599,7 +5709,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:21">
       <c r="A52" s="1" t="s">
         <v>396</v>
       </c>
@@ -5646,7 +5756,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:21">
       <c r="A53" s="1" t="s">
         <v>397</v>
       </c>
@@ -5690,7 +5800,7 @@
         <v>96.25</v>
       </c>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:21">
       <c r="A54" s="1" t="s">
         <v>398</v>
       </c>
@@ -5734,7 +5844,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:21">
       <c r="A55" s="1" t="s">
         <v>399</v>
       </c>
@@ -5783,8 +5893,14 @@
       <c r="S55">
         <v>75</v>
       </c>
-    </row>
-    <row r="56" spans="1:19">
+      <c r="T55" t="s">
+        <v>595</v>
+      </c>
+      <c r="U55">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
       <c r="A56" s="1" t="s">
         <v>400</v>
       </c>
@@ -5822,8 +5938,14 @@
       <c r="S56">
         <v>103</v>
       </c>
-    </row>
-    <row r="57" spans="1:19">
+      <c r="T56" t="s">
+        <v>596</v>
+      </c>
+      <c r="U56">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57" s="1" t="s">
         <v>400</v>
       </c>
@@ -5862,7 +5984,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:21">
       <c r="A58" s="1" t="s">
         <v>400</v>
       </c>
@@ -5909,7 +6031,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:21">
       <c r="A59" s="1" t="s">
         <v>400</v>
       </c>
@@ -5956,7 +6078,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:21">
       <c r="A60" s="1" t="s">
         <v>401</v>
       </c>
@@ -6000,7 +6122,7 @@
         <v>96.25</v>
       </c>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:21">
       <c r="A61" s="1" t="s">
         <v>402</v>
       </c>
@@ -6044,7 +6166,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:21">
       <c r="A62" s="1" t="s">
         <v>403</v>
       </c>
@@ -6093,8 +6215,14 @@
       <c r="S62">
         <v>75</v>
       </c>
-    </row>
-    <row r="63" spans="1:19">
+      <c r="T62" t="s">
+        <v>593</v>
+      </c>
+      <c r="U62">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63" s="1" t="s">
         <v>404</v>
       </c>
@@ -6132,8 +6260,14 @@
       <c r="S63">
         <v>103</v>
       </c>
-    </row>
-    <row r="64" spans="1:19">
+      <c r="T63" t="s">
+        <v>594</v>
+      </c>
+      <c r="U63">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64" s="1" t="s">
         <v>404</v>
       </c>
@@ -6172,7 +6306,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:21">
       <c r="A65" s="1" t="s">
         <v>404</v>
       </c>
@@ -6219,7 +6353,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:21">
       <c r="A66" s="1" t="s">
         <v>404</v>
       </c>
@@ -6266,7 +6400,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:21">
       <c r="A67" s="1" t="s">
         <v>405</v>
       </c>
@@ -6300,7 +6434,7 @@
       </c>
       <c r="N67" s="5"/>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:21">
       <c r="A68" s="1" t="s">
         <v>406</v>
       </c>
@@ -6335,7 +6469,7 @@
       <c r="N68" s="5"/>
       <c r="P68" s="2"/>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:21">
       <c r="A69" s="1" t="s">
         <v>407</v>
       </c>
@@ -6369,7 +6503,7 @@
       </c>
       <c r="N69" s="5"/>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:21">
       <c r="A70" s="1" t="s">
         <v>408</v>
       </c>
@@ -6403,7 +6537,7 @@
       </c>
       <c r="N70" s="5"/>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:21">
       <c r="A71" s="1" t="s">
         <v>408</v>
       </c>
@@ -6440,7 +6574,7 @@
       </c>
       <c r="N71" s="5"/>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:21">
       <c r="A72" s="1" t="s">
         <v>408</v>
       </c>
@@ -6477,7 +6611,7 @@
       </c>
       <c r="N72" s="5"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:21">
       <c r="A73" s="1" t="s">
         <v>409</v>
       </c>
@@ -6521,7 +6655,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:21">
       <c r="A74" s="1" t="s">
         <v>410</v>
       </c>
@@ -6565,7 +6699,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:21">
       <c r="A75" s="1" t="s">
         <v>411</v>
       </c>
@@ -6615,8 +6749,14 @@
         <f>I75-3</f>
         <v>104</v>
       </c>
-    </row>
-    <row r="76" spans="1:19">
+      <c r="T75" t="s">
+        <v>597</v>
+      </c>
+      <c r="U75">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
       <c r="A76" s="1" t="s">
         <v>412</v>
       </c>
@@ -6657,8 +6797,14 @@
         <f>I76</f>
         <v>145</v>
       </c>
-    </row>
-    <row r="77" spans="1:19">
+      <c r="T76" t="s">
+        <v>598</v>
+      </c>
+      <c r="U76">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
       <c r="A77" s="1" t="s">
         <v>412</v>
       </c>
@@ -6698,7 +6844,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:21">
       <c r="A78" s="1" t="s">
         <v>412</v>
       </c>
@@ -6724,7 +6870,7 @@
         <v>1.5</v>
       </c>
       <c r="I78" s="18">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>106</v>
@@ -6745,7 +6891,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:21">
       <c r="A79" s="1" t="s">
         <v>412</v>
       </c>
@@ -6771,7 +6917,7 @@
         <v>1.5</v>
       </c>
       <c r="I79" s="18">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>106</v>
@@ -6792,7 +6938,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:21">
       <c r="A80" s="1" t="s">
         <v>413</v>
       </c>
@@ -6836,7 +6982,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" spans="1:21">
       <c r="A81" s="1" t="s">
         <v>414</v>
       </c>
@@ -6880,7 +7026,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" spans="1:21">
       <c r="A82" s="1" t="s">
         <v>415</v>
       </c>
@@ -6930,8 +7076,14 @@
         <f>I82-3</f>
         <v>104</v>
       </c>
-    </row>
-    <row r="83" spans="1:19">
+      <c r="T82" t="s">
+        <v>601</v>
+      </c>
+      <c r="U82">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21">
       <c r="A83" s="1" t="s">
         <v>416</v>
       </c>
@@ -6972,8 +7124,14 @@
         <f>I83</f>
         <v>145</v>
       </c>
-    </row>
-    <row r="84" spans="1:19">
+      <c r="T83" t="s">
+        <v>602</v>
+      </c>
+      <c r="U83">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21">
       <c r="A84" s="1" t="s">
         <v>416</v>
       </c>
@@ -7013,7 +7171,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:21">
       <c r="A85" s="1" t="s">
         <v>416</v>
       </c>
@@ -7039,7 +7197,7 @@
         <v>1.5</v>
       </c>
       <c r="I85" s="18">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>109</v>
@@ -7060,7 +7218,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="86" spans="1:19">
+    <row r="86" spans="1:21">
       <c r="A86" s="1" t="s">
         <v>416</v>
       </c>
@@ -7086,7 +7244,7 @@
         <v>1.5</v>
       </c>
       <c r="I86" s="18">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J86" s="5" t="s">
         <v>109</v>
@@ -7107,7 +7265,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="87" spans="1:19">
+    <row r="87" spans="1:21">
       <c r="A87" s="1" t="s">
         <v>417</v>
       </c>
@@ -7130,7 +7288,7 @@
         <v>1.5</v>
       </c>
       <c r="I87" s="18">
-        <v>80</v>
+        <v>80.5</v>
       </c>
       <c r="J87" s="5" t="s">
         <v>110</v>
@@ -7151,7 +7309,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="88" spans="1:19">
+    <row r="88" spans="1:21">
       <c r="A88" s="1" t="s">
         <v>418</v>
       </c>
@@ -7195,7 +7353,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" spans="1:21">
       <c r="A89" s="1" t="s">
         <v>419</v>
       </c>
@@ -7245,8 +7403,14 @@
         <f>I89-3</f>
         <v>112</v>
       </c>
-    </row>
-    <row r="90" spans="1:19">
+      <c r="T89" t="s">
+        <v>603</v>
+      </c>
+      <c r="U89">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21">
       <c r="A90" s="1" t="s">
         <v>420</v>
       </c>
@@ -7287,8 +7451,14 @@
         <f>I90</f>
         <v>153</v>
       </c>
-    </row>
-    <row r="91" spans="1:19">
+      <c r="T90" t="s">
+        <v>604</v>
+      </c>
+      <c r="U90">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21">
       <c r="A91" s="1" t="s">
         <v>420</v>
       </c>
@@ -7328,7 +7498,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="92" spans="1:19">
+    <row r="92" spans="1:21">
       <c r="A92" s="1" t="s">
         <v>420</v>
       </c>
@@ -7375,7 +7545,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:21">
       <c r="A93" s="1" t="s">
         <v>420</v>
       </c>
@@ -7422,7 +7592,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="94" spans="1:19">
+    <row r="94" spans="1:21">
       <c r="A94" s="1" t="s">
         <v>421</v>
       </c>
@@ -7445,7 +7615,7 @@
         <v>1.5</v>
       </c>
       <c r="I94" s="18">
-        <v>82</v>
+        <v>82.5</v>
       </c>
       <c r="J94" s="5" t="s">
         <v>113</v>
@@ -7466,7 +7636,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="95" spans="1:19">
+    <row r="95" spans="1:21">
       <c r="A95" s="1" t="s">
         <v>422</v>
       </c>
@@ -7510,7 +7680,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="96" spans="1:19">
+    <row r="96" spans="1:21">
       <c r="A96" s="1" t="s">
         <v>423</v>
       </c>
@@ -7553,8 +7723,15 @@
       <c r="O96" s="2">
         <v>205</v>
       </c>
-    </row>
-    <row r="97" spans="1:19">
+      <c r="R96" s="14" t="s">
+        <v>947</v>
+      </c>
+      <c r="S96">
+        <f>I96-3</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21">
       <c r="A97" s="1" t="s">
         <v>424</v>
       </c>
@@ -7588,8 +7765,15 @@
       <c r="M97" s="2"/>
       <c r="N97"/>
       <c r="O97" s="2"/>
-    </row>
-    <row r="98" spans="1:19">
+      <c r="R97" s="14" t="s">
+        <v>948</v>
+      </c>
+      <c r="S97">
+        <f>I97</f>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21">
       <c r="A98" s="1" t="s">
         <v>424</v>
       </c>
@@ -7629,7 +7813,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="99" spans="1:19">
+    <row r="99" spans="1:21">
       <c r="A99" s="1" t="s">
         <v>424</v>
       </c>
@@ -7676,7 +7860,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="100" spans="1:19">
+    <row r="100" spans="1:21">
       <c r="A100" s="1" t="s">
         <v>424</v>
       </c>
@@ -7723,7 +7907,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="101" spans="1:19">
+    <row r="101" spans="1:21">
       <c r="A101" s="1" t="s">
         <v>425</v>
       </c>
@@ -7746,7 +7930,7 @@
         <v>1.5</v>
       </c>
       <c r="I101" s="18">
-        <v>82</v>
+        <v>82.5</v>
       </c>
       <c r="J101" s="5" t="s">
         <v>116</v>
@@ -7767,7 +7951,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="102" spans="1:19">
+    <row r="102" spans="1:21">
       <c r="A102" s="1" t="s">
         <v>426</v>
       </c>
@@ -7811,7 +7995,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="103" spans="1:19">
+    <row r="103" spans="1:21">
       <c r="A103" s="1" t="s">
         <v>427</v>
       </c>
@@ -7861,8 +8045,14 @@
         <f>I103-3</f>
         <v>113</v>
       </c>
-    </row>
-    <row r="104" spans="1:19">
+      <c r="T103" t="s">
+        <v>599</v>
+      </c>
+      <c r="U103">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21">
       <c r="A104" s="1" t="s">
         <v>428</v>
       </c>
@@ -7903,8 +8093,14 @@
         <f>I104</f>
         <v>157</v>
       </c>
-    </row>
-    <row r="105" spans="1:19">
+      <c r="T104" t="s">
+        <v>600</v>
+      </c>
+      <c r="U104">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21">
       <c r="A105" s="1" t="s">
         <v>428</v>
       </c>
@@ -7944,7 +8140,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="106" spans="1:19">
+    <row r="106" spans="1:21">
       <c r="A106" s="1" t="s">
         <v>428</v>
       </c>
@@ -7991,7 +8187,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="107" spans="1:19">
+    <row r="107" spans="1:21">
       <c r="A107" s="1" t="s">
         <v>428</v>
       </c>
@@ -8038,7 +8234,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="108" spans="1:19">
+    <row r="108" spans="1:21">
       <c r="A108" s="1" t="s">
         <v>429</v>
       </c>
@@ -8082,7 +8278,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="109" spans="1:19">
+    <row r="109" spans="1:21">
       <c r="A109" s="1" t="s">
         <v>430</v>
       </c>
@@ -8126,7 +8322,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="110" spans="1:19">
+    <row r="110" spans="1:21">
       <c r="A110" s="1" t="s">
         <v>431</v>
       </c>
@@ -8176,8 +8372,14 @@
         <f>I110-3</f>
         <v>113</v>
       </c>
-    </row>
-    <row r="111" spans="1:19">
+      <c r="T110" t="s">
+        <v>609</v>
+      </c>
+      <c r="U110">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21">
       <c r="A111" s="1" t="s">
         <v>432</v>
       </c>
@@ -8218,8 +8420,14 @@
         <f>I111</f>
         <v>157</v>
       </c>
-    </row>
-    <row r="112" spans="1:19">
+      <c r="T111" t="s">
+        <v>610</v>
+      </c>
+      <c r="U111">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21">
       <c r="A112" s="1" t="s">
         <v>432</v>
       </c>
@@ -8259,7 +8467,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="113" spans="1:19">
+    <row r="113" spans="1:21">
       <c r="A113" s="1" t="s">
         <v>432</v>
       </c>
@@ -8306,7 +8514,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="114" spans="1:19">
+    <row r="114" spans="1:21">
       <c r="A114" s="1" t="s">
         <v>432</v>
       </c>
@@ -8353,7 +8561,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="115" spans="1:19">
+    <row r="115" spans="1:21">
       <c r="A115" s="1" t="s">
         <v>433</v>
       </c>
@@ -8397,7 +8605,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="116" spans="1:19">
+    <row r="116" spans="1:21">
       <c r="A116" s="1" t="s">
         <v>434</v>
       </c>
@@ -8441,7 +8649,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="117" spans="1:19">
+    <row r="117" spans="1:21">
       <c r="A117" s="1" t="s">
         <v>435</v>
       </c>
@@ -8491,8 +8699,14 @@
         <f>I117-3</f>
         <v>118</v>
       </c>
-    </row>
-    <row r="118" spans="1:19">
+      <c r="T117" t="s">
+        <v>607</v>
+      </c>
+      <c r="U117">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21">
       <c r="A118" s="1" t="s">
         <v>436</v>
       </c>
@@ -8533,8 +8747,14 @@
         <f>I118</f>
         <v>165</v>
       </c>
-    </row>
-    <row r="119" spans="1:19">
+      <c r="T118" t="s">
+        <v>608</v>
+      </c>
+      <c r="U118">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21">
       <c r="A119" s="1" t="s">
         <v>436</v>
       </c>
@@ -8574,7 +8794,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="120" spans="1:19">
+    <row r="120" spans="1:21">
       <c r="A120" s="1" t="s">
         <v>436</v>
       </c>
@@ -8621,7 +8841,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="121" spans="1:19">
+    <row r="121" spans="1:21">
       <c r="A121" s="1" t="s">
         <v>436</v>
       </c>
@@ -8668,7 +8888,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="122" spans="1:19">
+    <row r="122" spans="1:21">
       <c r="A122" s="1" t="s">
         <v>437</v>
       </c>
@@ -8713,7 +8933,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="123" spans="1:19">
+    <row r="123" spans="1:21">
       <c r="A123" s="1" t="s">
         <v>438</v>
       </c>
@@ -8757,7 +8977,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="124" spans="1:19">
+    <row r="124" spans="1:21">
       <c r="A124" s="1" t="s">
         <v>439</v>
       </c>
@@ -8807,8 +9027,14 @@
         <f>I124-3</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="125" spans="1:19">
+      <c r="T124" t="s">
+        <v>605</v>
+      </c>
+      <c r="U124">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21">
       <c r="A125" s="1" t="s">
         <v>440</v>
       </c>
@@ -8849,8 +9075,14 @@
         <f>I125</f>
         <v>171</v>
       </c>
-    </row>
-    <row r="126" spans="1:19">
+      <c r="T125" t="s">
+        <v>606</v>
+      </c>
+      <c r="U125">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21">
       <c r="A126" s="1" t="s">
         <v>440</v>
       </c>
@@ -8890,7 +9122,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="127" spans="1:19">
+    <row r="127" spans="1:21">
       <c r="A127" s="1" t="s">
         <v>440</v>
       </c>
@@ -8937,7 +9169,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="128" spans="1:19">
+    <row r="128" spans="1:21">
       <c r="A128" s="1" t="s">
         <v>440</v>
       </c>
@@ -8984,7 +9216,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="129" spans="1:19">
+    <row r="129" spans="1:21">
       <c r="A129" s="5" t="s">
         <v>556</v>
       </c>
@@ -9020,7 +9252,7 @@
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
     </row>
-    <row r="130" spans="1:19">
+    <row r="130" spans="1:21">
       <c r="A130" s="5" t="s">
         <v>557</v>
       </c>
@@ -9056,7 +9288,7 @@
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
     </row>
-    <row r="131" spans="1:19">
+    <row r="131" spans="1:21">
       <c r="A131" s="5" t="s">
         <v>558</v>
       </c>
@@ -9098,8 +9330,14 @@
         <f>I131-3</f>
         <v>168</v>
       </c>
-    </row>
-    <row r="132" spans="1:19">
+      <c r="T131" t="s">
+        <v>611</v>
+      </c>
+      <c r="U131">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21">
       <c r="A132" s="5" t="s">
         <v>559</v>
       </c>
@@ -9141,8 +9379,14 @@
         <f>I132-4</f>
         <v>235</v>
       </c>
-    </row>
-    <row r="133" spans="1:19">
+      <c r="T132" t="s">
+        <v>612</v>
+      </c>
+      <c r="U132">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21">
       <c r="A133" s="5" t="s">
         <v>559</v>
       </c>
@@ -9181,7 +9425,7 @@
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
     </row>
-    <row r="134" spans="1:19">
+    <row r="134" spans="1:21">
       <c r="A134" s="5" t="s">
         <v>559</v>
       </c>
@@ -9220,7 +9464,7 @@
       <c r="N134" s="5"/>
       <c r="O134" s="2"/>
     </row>
-    <row r="135" spans="1:19">
+    <row r="135" spans="1:21">
       <c r="A135" s="5" t="s">
         <v>560</v>
       </c>
@@ -9254,7 +9498,7 @@
       <c r="N135" s="5"/>
       <c r="O135" s="2"/>
     </row>
-    <row r="136" spans="1:19">
+    <row r="136" spans="1:21">
       <c r="A136" s="5" t="s">
         <v>561</v>
       </c>
@@ -9288,7 +9532,7 @@
       <c r="N136" s="5"/>
       <c r="O136" s="2"/>
     </row>
-    <row r="137" spans="1:19">
+    <row r="137" spans="1:21">
       <c r="A137" s="5" t="s">
         <v>562</v>
       </c>
@@ -9328,8 +9572,14 @@
         <f>I137-3</f>
         <v>168</v>
       </c>
-    </row>
-    <row r="138" spans="1:19">
+      <c r="T137" t="s">
+        <v>644</v>
+      </c>
+      <c r="U137">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21">
       <c r="A138" s="5" t="s">
         <v>563</v>
       </c>
@@ -9369,8 +9619,14 @@
         <f>I138-4</f>
         <v>235</v>
       </c>
-    </row>
-    <row r="139" spans="1:19">
+      <c r="T138" t="s">
+        <v>645</v>
+      </c>
+      <c r="U138">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21">
       <c r="A139" s="5" t="s">
         <v>563</v>
       </c>
@@ -9407,7 +9663,7 @@
       <c r="N139" s="5"/>
       <c r="O139" s="2"/>
     </row>
-    <row r="140" spans="1:19">
+    <row r="140" spans="1:21">
       <c r="A140" s="5" t="s">
         <v>563</v>
       </c>
@@ -9444,7 +9700,7 @@
       <c r="N140" s="5"/>
       <c r="O140" s="2"/>
     </row>
-    <row r="141" spans="1:19">
+    <row r="141" spans="1:21">
       <c r="A141" s="5" t="s">
         <v>564</v>
       </c>
@@ -9478,7 +9734,7 @@
       <c r="N141" s="5"/>
       <c r="O141" s="2"/>
     </row>
-    <row r="142" spans="1:19">
+    <row r="142" spans="1:21">
       <c r="A142" s="5" t="s">
         <v>565</v>
       </c>
@@ -9512,7 +9768,7 @@
       <c r="N142" s="5"/>
       <c r="O142" s="2"/>
     </row>
-    <row r="143" spans="1:19">
+    <row r="143" spans="1:21">
       <c r="A143" s="5" t="s">
         <v>566</v>
       </c>
@@ -9552,8 +9808,14 @@
         <f>I143-3</f>
         <v>168</v>
       </c>
-    </row>
-    <row r="144" spans="1:19">
+      <c r="T143" t="s">
+        <v>646</v>
+      </c>
+      <c r="U143">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21">
       <c r="A144" s="5" t="s">
         <v>567</v>
       </c>
@@ -9593,8 +9855,14 @@
         <f>I144-4</f>
         <v>235</v>
       </c>
-    </row>
-    <row r="145" spans="1:19">
+      <c r="T144" t="s">
+        <v>647</v>
+      </c>
+      <c r="U144">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21">
       <c r="A145" s="5" t="s">
         <v>567</v>
       </c>
@@ -9631,7 +9899,7 @@
       <c r="N145" s="5"/>
       <c r="O145" s="2"/>
     </row>
-    <row r="146" spans="1:19">
+    <row r="146" spans="1:21">
       <c r="A146" s="5" t="s">
         <v>567</v>
       </c>
@@ -9668,7 +9936,7 @@
       <c r="N146" s="5"/>
       <c r="O146" s="2"/>
     </row>
-    <row r="147" spans="1:19">
+    <row r="147" spans="1:21">
       <c r="A147" s="5" t="s">
         <v>568</v>
       </c>
@@ -9702,7 +9970,7 @@
       <c r="N147" s="5"/>
       <c r="O147" s="2"/>
     </row>
-    <row r="148" spans="1:19">
+    <row r="148" spans="1:21">
       <c r="A148" s="5" t="s">
         <v>569</v>
       </c>
@@ -9736,7 +10004,7 @@
       <c r="N148"/>
       <c r="O148" s="2"/>
     </row>
-    <row r="149" spans="1:19">
+    <row r="149" spans="1:21">
       <c r="A149" s="5" t="s">
         <v>570</v>
       </c>
@@ -9771,7 +10039,7 @@
       <c r="O149" s="2"/>
       <c r="R149" s="5"/>
     </row>
-    <row r="150" spans="1:19">
+    <row r="150" spans="1:21">
       <c r="A150" s="5" t="s">
         <v>571</v>
       </c>
@@ -9806,7 +10074,7 @@
       <c r="O150" s="2"/>
       <c r="R150" s="5"/>
     </row>
-    <row r="151" spans="1:19">
+    <row r="151" spans="1:21">
       <c r="A151" s="5" t="s">
         <v>571</v>
       </c>
@@ -9843,7 +10111,7 @@
       <c r="N151" s="5"/>
       <c r="O151" s="2"/>
     </row>
-    <row r="152" spans="1:19">
+    <row r="152" spans="1:21">
       <c r="A152" s="5" t="s">
         <v>571</v>
       </c>
@@ -9880,7 +10148,7 @@
       <c r="N152" s="5"/>
       <c r="O152" s="2"/>
     </row>
-    <row r="153" spans="1:19">
+    <row r="153" spans="1:21">
       <c r="A153" s="5" t="s">
         <v>613</v>
       </c>
@@ -9914,7 +10182,7 @@
       <c r="N153" s="5"/>
       <c r="O153" s="2"/>
     </row>
-    <row r="154" spans="1:19">
+    <row r="154" spans="1:21">
       <c r="A154" s="5" t="s">
         <v>615</v>
       </c>
@@ -9948,7 +10216,7 @@
       <c r="N154" s="5"/>
       <c r="O154" s="2"/>
     </row>
-    <row r="155" spans="1:19">
+    <row r="155" spans="1:21">
       <c r="A155" s="5" t="s">
         <v>617</v>
       </c>
@@ -9988,8 +10256,14 @@
         <f>I155-3</f>
         <v>168</v>
       </c>
-    </row>
-    <row r="156" spans="1:19">
+      <c r="T155" t="s">
+        <v>648</v>
+      </c>
+      <c r="U155">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21">
       <c r="A156" s="5" t="s">
         <v>619</v>
       </c>
@@ -10029,8 +10303,14 @@
         <f>I156-4</f>
         <v>235</v>
       </c>
-    </row>
-    <row r="157" spans="1:19">
+      <c r="T156" t="s">
+        <v>649</v>
+      </c>
+      <c r="U156">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21">
       <c r="A157" s="5" t="s">
         <v>619</v>
       </c>
@@ -10067,7 +10347,7 @@
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
     </row>
-    <row r="158" spans="1:19">
+    <row r="158" spans="1:21">
       <c r="A158" s="5" t="s">
         <v>619</v>
       </c>
@@ -10104,7 +10384,7 @@
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
     </row>
-    <row r="159" spans="1:19">
+    <row r="159" spans="1:21">
       <c r="A159" s="5" t="s">
         <v>572</v>
       </c>
@@ -10138,7 +10418,7 @@
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
     </row>
-    <row r="160" spans="1:19">
+    <row r="160" spans="1:21">
       <c r="A160" s="5" t="s">
         <v>573</v>
       </c>
@@ -10172,7 +10452,7 @@
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
     </row>
-    <row r="161" spans="1:19">
+    <row r="161" spans="1:21">
       <c r="A161" s="5" t="s">
         <v>574</v>
       </c>
@@ -10212,8 +10492,14 @@
         <f>I161-3</f>
         <v>168</v>
       </c>
-    </row>
-    <row r="162" spans="1:19">
+      <c r="T161" t="s">
+        <v>650</v>
+      </c>
+      <c r="U161">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="162" spans="1:21">
       <c r="A162" s="5" t="s">
         <v>575</v>
       </c>
@@ -10253,8 +10539,14 @@
         <f>I162-4</f>
         <v>235</v>
       </c>
-    </row>
-    <row r="163" spans="1:19">
+      <c r="T162" t="s">
+        <v>651</v>
+      </c>
+      <c r="U162">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="163" spans="1:21">
       <c r="A163" s="5" t="s">
         <v>575</v>
       </c>
@@ -10291,7 +10583,7 @@
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
     </row>
-    <row r="164" spans="1:19">
+    <row r="164" spans="1:21">
       <c r="A164" s="5" t="s">
         <v>575</v>
       </c>
@@ -10328,7 +10620,7 @@
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
     </row>
-    <row r="165" spans="1:19">
+    <row r="165" spans="1:21">
       <c r="A165" s="5" t="s">
         <v>576</v>
       </c>
@@ -10362,7 +10654,7 @@
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
     </row>
-    <row r="166" spans="1:19">
+    <row r="166" spans="1:21">
       <c r="A166" s="5" t="s">
         <v>577</v>
       </c>
@@ -10396,7 +10688,7 @@
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
     </row>
-    <row r="167" spans="1:19">
+    <row r="167" spans="1:21">
       <c r="A167" s="5" t="s">
         <v>578</v>
       </c>
@@ -10436,8 +10728,14 @@
         <f>I167-3</f>
         <v>174</v>
       </c>
-    </row>
-    <row r="168" spans="1:19">
+      <c r="T167" t="s">
+        <v>652</v>
+      </c>
+      <c r="U167">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="168" spans="1:21">
       <c r="A168" s="5" t="s">
         <v>579</v>
       </c>
@@ -10477,8 +10775,14 @@
         <f>I168-4</f>
         <v>244</v>
       </c>
-    </row>
-    <row r="169" spans="1:19">
+      <c r="T168" t="s">
+        <v>653</v>
+      </c>
+      <c r="U168">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="169" spans="1:21">
       <c r="A169" s="5" t="s">
         <v>579</v>
       </c>
@@ -10515,7 +10819,7 @@
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
     </row>
-    <row r="170" spans="1:19">
+    <row r="170" spans="1:21">
       <c r="A170" s="5" t="s">
         <v>579</v>
       </c>
@@ -10552,7 +10856,7 @@
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
     </row>
-    <row r="171" spans="1:19">
+    <row r="171" spans="1:21">
       <c r="A171" s="5" t="s">
         <v>580</v>
       </c>
@@ -10586,7 +10890,7 @@
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
     </row>
-    <row r="172" spans="1:19">
+    <row r="172" spans="1:21">
       <c r="A172" s="5" t="s">
         <v>581</v>
       </c>
@@ -10620,7 +10924,7 @@
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
     </row>
-    <row r="173" spans="1:19">
+    <row r="173" spans="1:21">
       <c r="A173" s="5" t="s">
         <v>582</v>
       </c>
@@ -10660,8 +10964,14 @@
         <f>I173-3</f>
         <v>167</v>
       </c>
-    </row>
-    <row r="174" spans="1:19">
+      <c r="T173" t="s">
+        <v>654</v>
+      </c>
+      <c r="U173">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="174" spans="1:21">
       <c r="A174" s="5" t="s">
         <v>583</v>
       </c>
@@ -10701,8 +11011,14 @@
         <f>I174-4</f>
         <v>232</v>
       </c>
-    </row>
-    <row r="175" spans="1:19">
+      <c r="T174" t="s">
+        <v>655</v>
+      </c>
+      <c r="U174">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="175" spans="1:21">
       <c r="A175" s="5" t="s">
         <v>583</v>
       </c>
@@ -10739,7 +11055,7 @@
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
     </row>
-    <row r="176" spans="1:19">
+    <row r="176" spans="1:21">
       <c r="A176" s="5" t="s">
         <v>583</v>
       </c>
@@ -12485,6 +12801,9 @@
       <c r="M225" s="3">
         <v>650</v>
       </c>
+      <c r="O225" s="3">
+        <v>635</v>
+      </c>
       <c r="R225" s="5" t="s">
         <v>656</v>
       </c>
@@ -12494,63 +12813,64 @@
     </row>
     <row r="226" spans="1:19">
       <c r="A226" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B226" s="6" t="s">
-        <v>209</v>
+        <v>940</v>
+      </c>
+      <c r="B226" s="17" t="s">
+        <v>941</v>
       </c>
       <c r="G226" s="3">
         <v>50</v>
       </c>
       <c r="I226" s="2">
-        <v>480</v>
-      </c>
-      <c r="J226" s="6" t="s">
-        <v>205</v>
+        <v>520</v>
+      </c>
+      <c r="J226" s="17" t="s">
+        <v>942</v>
       </c>
       <c r="K226" s="2">
-        <v>630</v>
-      </c>
-      <c r="L226" s="5" t="s">
-        <v>657</v>
-      </c>
-      <c r="M226" s="3">
-        <v>700</v>
+        <v>685</v>
+      </c>
+      <c r="L226" s="5"/>
+      <c r="O226" s="3">
+        <v>760</v>
       </c>
       <c r="R226" s="5" t="s">
-        <v>657</v>
+        <v>943</v>
       </c>
       <c r="S226">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="227" spans="1:19">
       <c r="A227" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G227" s="3">
         <v>50</v>
       </c>
       <c r="I227" s="2">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="J227" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K227" s="2">
-        <v>710</v>
+        <v>630</v>
       </c>
       <c r="L227" s="5" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="M227" s="3">
-        <v>775</v>
+        <v>700</v>
+      </c>
+      <c r="O227" s="3">
+        <v>675</v>
       </c>
       <c r="R227" s="5" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="S227">
         <v>480</v>
@@ -12558,72 +12878,77 @@
     </row>
     <row r="228" spans="1:19">
       <c r="A228" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G228" s="3">
         <v>50</v>
       </c>
       <c r="I228" s="2">
+        <v>510</v>
+      </c>
+      <c r="J228" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="K228" s="2">
+        <v>710</v>
+      </c>
+      <c r="L228" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="M228" s="3">
+        <v>775</v>
+      </c>
+      <c r="O228" s="3">
+        <v>760</v>
+      </c>
+      <c r="R228" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="S228">
         <v>480</v>
-      </c>
-      <c r="J228" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="K228" s="2">
-        <v>675</v>
-      </c>
-      <c r="L228" s="5" t="s">
-        <v>659</v>
-      </c>
-      <c r="M228" s="3">
-        <v>735</v>
-      </c>
-      <c r="R228" s="5" t="s">
-        <v>659</v>
-      </c>
-      <c r="S228">
-        <v>510</v>
       </c>
     </row>
     <row r="229" spans="1:19">
       <c r="A229" s="5" t="s">
-        <v>441</v>
+        <v>203</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C229" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="D229" s="2">
-        <v>5</v>
-      </c>
-      <c r="E229" s="2">
-        <v>40</v>
-      </c>
-      <c r="F229" s="2"/>
+        <v>211</v>
+      </c>
       <c r="G229" s="3">
-        <v>100</v>
-      </c>
-      <c r="H229" s="3">
-        <v>1.5</v>
+        <v>50</v>
       </c>
       <c r="I229" s="2">
-        <v>169.3</v>
-      </c>
-      <c r="P229" s="6" t="s">
-        <v>696</v>
-      </c>
-      <c r="Q229" s="2">
-        <v>280</v>
+        <v>480</v>
+      </c>
+      <c r="J229" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="K229" s="2">
+        <v>675</v>
+      </c>
+      <c r="L229" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="M229" s="3">
+        <v>735</v>
+      </c>
+      <c r="O229" s="3">
+        <v>725</v>
+      </c>
+      <c r="R229" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="S229">
+        <v>510</v>
       </c>
     </row>
     <row r="230" spans="1:19">
       <c r="A230" s="5" t="s">
-        <v>867</v>
+        <v>441</v>
       </c>
       <c r="B230" s="6" t="s">
         <v>361</v>
@@ -12639,27 +12964,27 @@
       </c>
       <c r="F230" s="2"/>
       <c r="G230" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H230" s="3">
         <v>1.5</v>
       </c>
       <c r="I230" s="2">
-        <v>93.65</v>
-      </c>
-      <c r="P230" s="17" t="s">
-        <v>871</v>
+        <v>169.3</v>
+      </c>
+      <c r="P230" s="6" t="s">
+        <v>696</v>
       </c>
       <c r="Q230" s="2">
-        <v>150</v>
+        <v>280</v>
       </c>
     </row>
     <row r="231" spans="1:19">
       <c r="A231" s="5" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C231" s="6" t="s">
         <v>503</v>
@@ -12668,7 +12993,7 @@
         <v>5</v>
       </c>
       <c r="E231" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F231" s="2"/>
       <c r="G231" s="3">
@@ -12678,51 +13003,51 @@
         <v>1.5</v>
       </c>
       <c r="I231" s="2">
-        <v>129.35</v>
-      </c>
-      <c r="P231" s="16" t="s">
-        <v>872</v>
+        <v>93.65</v>
+      </c>
+      <c r="P231" s="17" t="s">
+        <v>871</v>
       </c>
       <c r="Q231" s="2">
-        <v>215</v>
+        <v>150</v>
       </c>
     </row>
     <row r="232" spans="1:19">
       <c r="A232" s="5" t="s">
-        <v>442</v>
+        <v>868</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D232" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E232" s="2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F232" s="2"/>
       <c r="G232" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H232" s="3">
         <v>1.5</v>
       </c>
       <c r="I232" s="2">
-        <v>169.3</v>
-      </c>
-      <c r="P232" s="6" t="s">
-        <v>697</v>
+        <v>129.35</v>
+      </c>
+      <c r="P232" s="16" t="s">
+        <v>872</v>
       </c>
       <c r="Q232" s="2">
-        <v>280</v>
+        <v>215</v>
       </c>
     </row>
     <row r="233" spans="1:19">
       <c r="A233" s="5" t="s">
-        <v>931</v>
+        <v>442</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>363</v>
@@ -12738,27 +13063,27 @@
       </c>
       <c r="F233" s="2"/>
       <c r="G233" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H233" s="3">
         <v>1.5</v>
       </c>
       <c r="I233" s="2">
-        <v>93.65</v>
-      </c>
-      <c r="P233" s="17" t="s">
-        <v>869</v>
+        <v>169.3</v>
+      </c>
+      <c r="P233" s="6" t="s">
+        <v>697</v>
       </c>
       <c r="Q233" s="2">
-        <v>150</v>
+        <v>280</v>
       </c>
     </row>
     <row r="234" spans="1:19">
       <c r="A234" s="5" t="s">
-        <v>870</v>
+        <v>931</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C234" s="6" t="s">
         <v>504</v>
@@ -12767,7 +13092,7 @@
         <v>15</v>
       </c>
       <c r="E234" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F234" s="2"/>
       <c r="G234" s="3">
@@ -12777,51 +13102,51 @@
         <v>1.5</v>
       </c>
       <c r="I234" s="2">
-        <v>129.35</v>
-      </c>
-      <c r="P234" s="16" t="s">
-        <v>874</v>
+        <v>93.65</v>
+      </c>
+      <c r="P234" s="17" t="s">
+        <v>869</v>
       </c>
       <c r="Q234" s="2">
-        <v>215</v>
+        <v>150</v>
       </c>
     </row>
     <row r="235" spans="1:19">
       <c r="A235" s="5" t="s">
-        <v>443</v>
+        <v>870</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D235" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E235" s="2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F235" s="2"/>
       <c r="G235" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H235" s="3">
         <v>1.5</v>
       </c>
       <c r="I235" s="2">
-        <v>169.3</v>
-      </c>
-      <c r="P235" s="6" t="s">
-        <v>698</v>
+        <v>129.35</v>
+      </c>
+      <c r="P235" s="16" t="s">
+        <v>874</v>
       </c>
       <c r="Q235" s="2">
-        <v>280</v>
+        <v>215</v>
       </c>
     </row>
     <row r="236" spans="1:19">
       <c r="A236" s="5" t="s">
-        <v>932</v>
+        <v>443</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>365</v>
@@ -12837,27 +13162,27 @@
       </c>
       <c r="F236" s="2"/>
       <c r="G236" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H236" s="3">
         <v>1.5</v>
       </c>
       <c r="I236" s="2">
-        <v>93.65</v>
-      </c>
-      <c r="P236" s="17" t="s">
-        <v>936</v>
+        <v>169.3</v>
+      </c>
+      <c r="P236" s="6" t="s">
+        <v>698</v>
       </c>
       <c r="Q236" s="2">
-        <v>150</v>
+        <v>280</v>
       </c>
     </row>
     <row r="237" spans="1:19">
       <c r="A237" s="5" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C237" s="6" t="s">
         <v>505</v>
@@ -12866,7 +13191,7 @@
         <v>20</v>
       </c>
       <c r="E237" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F237" s="2"/>
       <c r="G237" s="3">
@@ -12876,51 +13201,51 @@
         <v>1.5</v>
       </c>
       <c r="I237" s="2">
-        <v>129.35</v>
-      </c>
-      <c r="P237" s="16" t="s">
-        <v>873</v>
+        <v>93.65</v>
+      </c>
+      <c r="P237" s="17" t="s">
+        <v>936</v>
       </c>
       <c r="Q237" s="2">
-        <v>215</v>
+        <v>150</v>
       </c>
     </row>
     <row r="238" spans="1:19">
       <c r="A238" s="5" t="s">
-        <v>444</v>
+        <v>927</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>623</v>
+        <v>505</v>
       </c>
       <c r="D238" s="2">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E238" s="2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F238" s="2"/>
       <c r="G238" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H238" s="3">
         <v>1.5</v>
       </c>
       <c r="I238" s="2">
-        <v>169.3</v>
-      </c>
-      <c r="P238" s="17" t="s">
-        <v>699</v>
+        <v>129.35</v>
+      </c>
+      <c r="P238" s="16" t="s">
+        <v>873</v>
       </c>
       <c r="Q238" s="2">
-        <v>280</v>
+        <v>215</v>
       </c>
     </row>
     <row r="239" spans="1:19">
       <c r="A239" s="5" t="s">
-        <v>933</v>
+        <v>444</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>367</v>
@@ -12936,27 +13261,27 @@
       </c>
       <c r="F239" s="2"/>
       <c r="G239" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H239" s="3">
         <v>1.5</v>
       </c>
       <c r="I239" s="2">
-        <v>93.65</v>
+        <v>169.3</v>
       </c>
       <c r="P239" s="17" t="s">
-        <v>937</v>
+        <v>699</v>
       </c>
       <c r="Q239" s="2">
-        <v>150</v>
+        <v>280</v>
       </c>
     </row>
     <row r="240" spans="1:19">
       <c r="A240" s="5" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C240" s="6" t="s">
         <v>623</v>
@@ -12965,7 +13290,7 @@
         <v>35</v>
       </c>
       <c r="E240" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F240" s="2"/>
       <c r="G240" s="3">
@@ -12975,51 +13300,51 @@
         <v>1.5</v>
       </c>
       <c r="I240" s="2">
-        <v>129.35</v>
-      </c>
-      <c r="P240" s="16" t="s">
-        <v>924</v>
+        <v>93.65</v>
+      </c>
+      <c r="P240" s="17" t="s">
+        <v>937</v>
       </c>
       <c r="Q240" s="2">
-        <v>215</v>
+        <v>150</v>
       </c>
     </row>
     <row r="241" spans="1:17">
       <c r="A241" s="5" t="s">
-        <v>445</v>
+        <v>928</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>508</v>
+        <v>623</v>
       </c>
       <c r="D241" s="2">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E241" s="2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F241" s="2"/>
       <c r="G241" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H241" s="3">
         <v>1.5</v>
       </c>
       <c r="I241" s="2">
-        <v>175.3</v>
-      </c>
-      <c r="P241" s="6" t="s">
-        <v>700</v>
+        <v>129.35</v>
+      </c>
+      <c r="P241" s="16" t="s">
+        <v>924</v>
       </c>
       <c r="Q241" s="2">
-        <v>280</v>
+        <v>215</v>
       </c>
     </row>
     <row r="242" spans="1:17">
       <c r="A242" s="5" t="s">
-        <v>934</v>
+        <v>445</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>369</v>
@@ -13035,27 +13360,27 @@
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H242" s="3">
         <v>1.5</v>
       </c>
       <c r="I242" s="2">
-        <v>96.65</v>
-      </c>
-      <c r="P242" s="17" t="s">
-        <v>938</v>
+        <v>175.3</v>
+      </c>
+      <c r="P242" s="6" t="s">
+        <v>700</v>
       </c>
       <c r="Q242" s="2">
-        <v>150</v>
+        <v>280</v>
       </c>
     </row>
     <row r="243" spans="1:17">
       <c r="A243" s="5" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C243" s="6" t="s">
         <v>508</v>
@@ -13064,7 +13389,7 @@
         <v>50</v>
       </c>
       <c r="E243" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="3">
@@ -13074,51 +13399,51 @@
         <v>1.5</v>
       </c>
       <c r="I243" s="2">
-        <v>133.80000000000001</v>
-      </c>
-      <c r="P243" s="16" t="s">
-        <v>925</v>
+        <v>96.65</v>
+      </c>
+      <c r="P243" s="17" t="s">
+        <v>938</v>
       </c>
       <c r="Q243" s="2">
-        <v>215</v>
+        <v>150</v>
       </c>
     </row>
     <row r="244" spans="1:17">
       <c r="A244" s="5" t="s">
-        <v>446</v>
+        <v>929</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D244" s="2">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E244" s="2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H244" s="3">
         <v>1.5</v>
       </c>
       <c r="I244" s="2">
-        <v>168.3</v>
-      </c>
-      <c r="P244" s="6" t="s">
-        <v>701</v>
+        <v>133.80000000000001</v>
+      </c>
+      <c r="P244" s="16" t="s">
+        <v>925</v>
       </c>
       <c r="Q244" s="2">
-        <v>280</v>
+        <v>215</v>
       </c>
     </row>
     <row r="245" spans="1:17">
       <c r="A245" s="5" t="s">
-        <v>935</v>
+        <v>446</v>
       </c>
       <c r="B245" s="6" t="s">
         <v>371</v>
@@ -13134,27 +13459,27 @@
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H245" s="3">
         <v>1.5</v>
       </c>
       <c r="I245" s="2">
-        <v>93.15</v>
-      </c>
-      <c r="P245" s="17" t="s">
-        <v>939</v>
+        <v>168.3</v>
+      </c>
+      <c r="P245" s="6" t="s">
+        <v>701</v>
       </c>
       <c r="Q245" s="2">
-        <v>150</v>
+        <v>280</v>
       </c>
     </row>
     <row r="246" spans="1:17">
       <c r="A246" s="5" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C246" s="6" t="s">
         <v>509</v>
@@ -13163,7 +13488,7 @@
         <v>70</v>
       </c>
       <c r="E246" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F246" s="2"/>
       <c r="G246" s="3">
@@ -13173,54 +13498,54 @@
         <v>1.5</v>
       </c>
       <c r="I246" s="2">
-        <v>127.85</v>
-      </c>
-      <c r="P246" s="16" t="s">
-        <v>926</v>
+        <v>93.15</v>
+      </c>
+      <c r="P246" s="17" t="s">
+        <v>939</v>
       </c>
       <c r="Q246" s="2">
-        <v>215</v>
+        <v>150</v>
       </c>
     </row>
     <row r="247" spans="1:17">
       <c r="A247" s="5" t="s">
-        <v>212</v>
+        <v>930</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>282</v>
+        <v>372</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D247" s="2">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="E247" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F247" s="2"/>
       <c r="G247" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H247" s="3">
         <v>1.5</v>
       </c>
       <c r="I247" s="2">
-        <v>51</v>
-      </c>
-      <c r="P247" s="6" t="s">
-        <v>702</v>
+        <v>127.85</v>
+      </c>
+      <c r="P247" s="16" t="s">
+        <v>926</v>
       </c>
       <c r="Q247" s="2">
-        <v>63</v>
+        <v>215</v>
       </c>
     </row>
     <row r="248" spans="1:17">
       <c r="A248" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C248" s="6" t="s">
         <v>510</v>
@@ -13229,7 +13554,7 @@
         <v>5</v>
       </c>
       <c r="E248" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F248" s="2"/>
       <c r="G248" s="3">
@@ -13239,21 +13564,21 @@
         <v>1.5</v>
       </c>
       <c r="I248" s="2">
-        <v>73.3</v>
+        <v>51</v>
       </c>
       <c r="P248" s="6" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="Q248" s="2">
-        <v>91.35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="249" spans="1:17">
       <c r="A249" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C249" s="6" t="s">
         <v>510</v>
@@ -13262,7 +13587,7 @@
         <v>5</v>
       </c>
       <c r="E249" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F249" s="2"/>
       <c r="G249" s="3">
@@ -13275,7 +13600,7 @@
         <v>73.3</v>
       </c>
       <c r="P249" s="6" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="Q249" s="2">
         <v>91.35</v>
@@ -13283,10 +13608,10 @@
     </row>
     <row r="250" spans="1:17">
       <c r="A250" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C250" s="6" t="s">
         <v>510</v>
@@ -13294,12 +13619,10 @@
       <c r="D250" s="2">
         <v>5</v>
       </c>
-      <c r="E250" s="3">
-        <v>60</v>
-      </c>
-      <c r="F250" s="3" t="s">
-        <v>353</v>
-      </c>
+      <c r="E250" s="2">
+        <v>40</v>
+      </c>
+      <c r="F250" s="2"/>
       <c r="G250" s="3">
         <v>100</v>
       </c>
@@ -13307,13 +13630,13 @@
         <v>1.5</v>
       </c>
       <c r="I250" s="2">
-        <v>101</v>
+        <v>73.3</v>
       </c>
       <c r="P250" s="6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="Q250" s="2">
-        <v>126</v>
+        <v>91.35</v>
       </c>
     </row>
     <row r="251" spans="1:17">
@@ -13329,11 +13652,11 @@
       <c r="D251" s="2">
         <v>5</v>
       </c>
-      <c r="E251" s="2">
+      <c r="E251" s="3">
         <v>60</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G251" s="3">
         <v>100</v>
@@ -13367,8 +13690,8 @@
       <c r="E252" s="2">
         <v>60</v>
       </c>
-      <c r="F252" s="2" t="s">
-        <v>355</v>
+      <c r="F252" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="G252" s="3">
         <v>100</v>
@@ -13377,13 +13700,13 @@
         <v>1.5</v>
       </c>
       <c r="I252" s="2">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="P252" s="6" t="s">
         <v>705</v>
       </c>
       <c r="Q252" s="2">
-        <v>134.4</v>
+        <v>126</v>
       </c>
     </row>
     <row r="253" spans="1:17">
@@ -13403,7 +13726,7 @@
         <v>60</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G253" s="3">
         <v>100</v>
@@ -13438,7 +13761,7 @@
         <v>60</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G254" s="3">
         <v>100</v>
@@ -13447,13 +13770,13 @@
         <v>1.5</v>
       </c>
       <c r="I254" s="2">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="P254" s="6" t="s">
         <v>705</v>
       </c>
       <c r="Q254" s="2">
-        <v>142.80000000000001</v>
+        <v>134.4</v>
       </c>
     </row>
     <row r="255" spans="1:17">
@@ -13473,7 +13796,7 @@
         <v>60</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G255" s="3">
         <v>100</v>
@@ -13482,18 +13805,18 @@
         <v>1.5</v>
       </c>
       <c r="I255" s="2">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="P255" s="6" t="s">
         <v>705</v>
       </c>
       <c r="Q255" s="2">
-        <v>165.38</v>
+        <v>142.80000000000001</v>
       </c>
     </row>
     <row r="256" spans="1:17">
       <c r="A256" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>285</v>
@@ -13507,62 +13830,64 @@
       <c r="E256" s="2">
         <v>60</v>
       </c>
-      <c r="F256" s="2"/>
+      <c r="F256" s="2" t="s">
+        <v>358</v>
+      </c>
       <c r="G256" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H256" s="3">
         <v>1.5</v>
       </c>
       <c r="I256" s="2">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="P256" s="6" t="s">
-        <v>334</v>
+        <v>705</v>
       </c>
       <c r="Q256" s="2">
-        <v>71.400000000000006</v>
+        <v>165.38</v>
       </c>
     </row>
     <row r="257" spans="1:17">
       <c r="A257" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D257" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E257" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F257" s="2"/>
       <c r="G257" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H257" s="3">
         <v>1.5</v>
       </c>
       <c r="I257" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P257" s="6" t="s">
-        <v>706</v>
+        <v>334</v>
       </c>
       <c r="Q257" s="2">
-        <v>63</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="258" spans="1:17">
       <c r="A258" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C258" s="6" t="s">
         <v>511</v>
@@ -13571,7 +13896,7 @@
         <v>15</v>
       </c>
       <c r="E258" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F258" s="2"/>
       <c r="G258" s="3">
@@ -13581,21 +13906,21 @@
         <v>1.5</v>
       </c>
       <c r="I258" s="2">
-        <v>72.3</v>
+        <v>50</v>
       </c>
       <c r="P258" s="6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q258" s="2">
-        <v>91.35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="259" spans="1:17">
       <c r="A259" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C259" s="6" t="s">
         <v>511</v>
@@ -13604,7 +13929,7 @@
         <v>15</v>
       </c>
       <c r="E259" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F259" s="2"/>
       <c r="G259" s="3">
@@ -13617,7 +13942,7 @@
         <v>72.3</v>
       </c>
       <c r="P259" s="6" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="Q259" s="2">
         <v>91.35</v>
@@ -13625,10 +13950,10 @@
     </row>
     <row r="260" spans="1:17">
       <c r="A260" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C260" s="6" t="s">
         <v>511</v>
@@ -13637,11 +13962,9 @@
         <v>15</v>
       </c>
       <c r="E260" s="2">
-        <v>60</v>
-      </c>
-      <c r="F260" s="3" t="s">
-        <v>353</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F260" s="2"/>
       <c r="G260" s="3">
         <v>100</v>
       </c>
@@ -13649,13 +13972,13 @@
         <v>1.5</v>
       </c>
       <c r="I260" s="2">
-        <v>99</v>
+        <v>72.3</v>
       </c>
       <c r="P260" s="6" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="Q260" s="2">
-        <v>126</v>
+        <v>91.35</v>
       </c>
     </row>
     <row r="261" spans="1:17">
@@ -13675,7 +13998,7 @@
         <v>60</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G261" s="3">
         <v>100</v>
@@ -13695,7 +14018,7 @@
     </row>
     <row r="262" spans="1:17">
       <c r="A262" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B262" s="6" t="s">
         <v>289</v>
@@ -13709,62 +14032,64 @@
       <c r="E262" s="2">
         <v>60</v>
       </c>
-      <c r="F262" s="2"/>
+      <c r="F262" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="G262" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H262" s="3">
         <v>1.5</v>
       </c>
       <c r="I262" s="2">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="P262" s="6" t="s">
-        <v>335</v>
+        <v>709</v>
       </c>
       <c r="Q262" s="2">
-        <v>71.400000000000006</v>
+        <v>126</v>
       </c>
     </row>
     <row r="263" spans="1:17">
       <c r="A263" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D263" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E263" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F263" s="2"/>
       <c r="G263" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H263" s="3">
         <v>1.5</v>
       </c>
       <c r="I263" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="P263" s="6" t="s">
-        <v>710</v>
+        <v>335</v>
       </c>
       <c r="Q263" s="2">
-        <v>63</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="264" spans="1:17">
       <c r="A264" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C264" s="6" t="s">
         <v>512</v>
@@ -13773,7 +14098,7 @@
         <v>20</v>
       </c>
       <c r="E264" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F264" s="2"/>
       <c r="G264" s="3">
@@ -13783,21 +14108,21 @@
         <v>1.5</v>
       </c>
       <c r="I264" s="2">
-        <v>72.3</v>
+        <v>50</v>
       </c>
       <c r="P264" s="6" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="Q264" s="2">
-        <v>91.35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="265" spans="1:17">
       <c r="A265" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C265" s="6" t="s">
         <v>512</v>
@@ -13806,7 +14131,7 @@
         <v>20</v>
       </c>
       <c r="E265" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F265" s="2"/>
       <c r="G265" s="3">
@@ -13819,7 +14144,7 @@
         <v>72.3</v>
       </c>
       <c r="P265" s="6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="Q265" s="2">
         <v>91.35</v>
@@ -13827,10 +14152,10 @@
     </row>
     <row r="266" spans="1:17">
       <c r="A266" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C266" s="6" t="s">
         <v>512</v>
@@ -13839,11 +14164,9 @@
         <v>20</v>
       </c>
       <c r="E266" s="2">
-        <v>60</v>
-      </c>
-      <c r="F266" s="3" t="s">
-        <v>353</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F266" s="2"/>
       <c r="G266" s="3">
         <v>100</v>
       </c>
@@ -13851,13 +14174,13 @@
         <v>1.5</v>
       </c>
       <c r="I266" s="2">
-        <v>99</v>
+        <v>72.3</v>
       </c>
       <c r="P266" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="Q266" s="2">
-        <v>126</v>
+        <v>91.35</v>
       </c>
     </row>
     <row r="267" spans="1:17">
@@ -13877,7 +14200,7 @@
         <v>60</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G267" s="3">
         <v>100</v>
@@ -13897,7 +14220,7 @@
     </row>
     <row r="268" spans="1:17">
       <c r="A268" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>293</v>
@@ -13911,62 +14234,64 @@
       <c r="E268" s="2">
         <v>60</v>
       </c>
-      <c r="F268" s="2"/>
+      <c r="F268" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="G268" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H268" s="3">
         <v>1.5</v>
       </c>
       <c r="I268" s="2">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="P268" s="6" t="s">
-        <v>336</v>
+        <v>713</v>
       </c>
       <c r="Q268" s="2">
-        <v>71.400000000000006</v>
+        <v>126</v>
       </c>
     </row>
     <row r="269" spans="1:17">
       <c r="A269" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D269" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E269" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F269" s="2"/>
       <c r="G269" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H269" s="3">
         <v>1.5</v>
       </c>
       <c r="I269" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="P269" s="6" t="s">
-        <v>714</v>
+        <v>336</v>
       </c>
       <c r="Q269" s="2">
-        <v>63</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="270" spans="1:17">
       <c r="A270" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C270" s="6" t="s">
         <v>513</v>
@@ -13975,7 +14300,7 @@
         <v>25</v>
       </c>
       <c r="E270" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F270" s="2"/>
       <c r="G270" s="3">
@@ -13985,21 +14310,21 @@
         <v>1.5</v>
       </c>
       <c r="I270" s="2">
-        <v>72.3</v>
+        <v>50</v>
       </c>
       <c r="P270" s="6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Q270" s="2">
-        <v>91.35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="271" spans="1:17">
       <c r="A271" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C271" s="6" t="s">
         <v>513</v>
@@ -14008,7 +14333,7 @@
         <v>25</v>
       </c>
       <c r="E271" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F271" s="2"/>
       <c r="G271" s="3">
@@ -14021,7 +14346,7 @@
         <v>72.3</v>
       </c>
       <c r="P271" s="6" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="Q271" s="2">
         <v>91.35</v>
@@ -14029,10 +14354,10 @@
     </row>
     <row r="272" spans="1:17">
       <c r="A272" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C272" s="6" t="s">
         <v>513</v>
@@ -14041,11 +14366,9 @@
         <v>25</v>
       </c>
       <c r="E272" s="2">
-        <v>60</v>
-      </c>
-      <c r="F272" s="3" t="s">
-        <v>353</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F272" s="2"/>
       <c r="G272" s="3">
         <v>100</v>
       </c>
@@ -14053,13 +14376,13 @@
         <v>1.5</v>
       </c>
       <c r="I272" s="2">
-        <v>99</v>
+        <v>72.3</v>
       </c>
       <c r="P272" s="6" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="Q272" s="2">
-        <v>126</v>
+        <v>91.35</v>
       </c>
     </row>
     <row r="273" spans="1:17">
@@ -14079,7 +14402,7 @@
         <v>60</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G273" s="3">
         <v>100</v>
@@ -14099,7 +14422,7 @@
     </row>
     <row r="274" spans="1:17">
       <c r="A274" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>297</v>
@@ -14113,62 +14436,64 @@
       <c r="E274" s="2">
         <v>60</v>
       </c>
-      <c r="F274" s="2"/>
+      <c r="F274" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="G274" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H274" s="3">
         <v>1.5</v>
       </c>
       <c r="I274" s="2">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="P274" s="6" t="s">
-        <v>337</v>
+        <v>717</v>
       </c>
       <c r="Q274" s="2">
-        <v>71.400000000000006</v>
+        <v>126</v>
       </c>
     </row>
     <row r="275" spans="1:17">
       <c r="A275" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D275" s="2">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E275" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F275" s="2"/>
       <c r="G275" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H275" s="3">
         <v>1.5</v>
       </c>
       <c r="I275" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="P275" s="6" t="s">
-        <v>718</v>
+        <v>337</v>
       </c>
       <c r="Q275" s="2">
-        <v>63</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="276" spans="1:17">
       <c r="A276" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C276" s="6" t="s">
         <v>514</v>
@@ -14177,7 +14502,7 @@
         <v>35</v>
       </c>
       <c r="E276" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F276" s="2"/>
       <c r="G276" s="3">
@@ -14187,21 +14512,21 @@
         <v>1.5</v>
       </c>
       <c r="I276" s="2">
-        <v>72.3</v>
+        <v>50</v>
       </c>
       <c r="P276" s="6" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="Q276" s="2">
-        <v>91.35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="277" spans="1:17">
       <c r="A277" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C277" s="6" t="s">
         <v>514</v>
@@ -14210,7 +14535,7 @@
         <v>35</v>
       </c>
       <c r="E277" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F277" s="2"/>
       <c r="G277" s="3">
@@ -14223,7 +14548,7 @@
         <v>72.3</v>
       </c>
       <c r="P277" s="6" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="Q277" s="2">
         <v>91.35</v>
@@ -14231,10 +14556,10 @@
     </row>
     <row r="278" spans="1:17">
       <c r="A278" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C278" s="6" t="s">
         <v>514</v>
@@ -14243,11 +14568,9 @@
         <v>35</v>
       </c>
       <c r="E278" s="2">
-        <v>60</v>
-      </c>
-      <c r="F278" s="3" t="s">
-        <v>353</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F278" s="2"/>
       <c r="G278" s="3">
         <v>100</v>
       </c>
@@ -14255,13 +14578,13 @@
         <v>1.5</v>
       </c>
       <c r="I278" s="2">
-        <v>99</v>
+        <v>72.3</v>
       </c>
       <c r="P278" s="6" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="Q278" s="2">
-        <v>126</v>
+        <v>91.35</v>
       </c>
     </row>
     <row r="279" spans="1:17">
@@ -14281,7 +14604,7 @@
         <v>60</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G279" s="3">
         <v>100</v>
@@ -14301,7 +14624,7 @@
     </row>
     <row r="280" spans="1:17">
       <c r="A280" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B280" s="6" t="s">
         <v>301</v>
@@ -14315,62 +14638,64 @@
       <c r="E280" s="2">
         <v>60</v>
       </c>
-      <c r="F280" s="2"/>
+      <c r="F280" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="G280" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H280" s="3">
         <v>1.5</v>
       </c>
       <c r="I280" s="2">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="P280" s="6" t="s">
-        <v>338</v>
+        <v>721</v>
       </c>
       <c r="Q280" s="2">
-        <v>71.400000000000006</v>
+        <v>126</v>
       </c>
     </row>
     <row r="281" spans="1:17">
       <c r="A281" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D281" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E281" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F281" s="2"/>
       <c r="G281" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H281" s="3">
         <v>1.5</v>
       </c>
       <c r="I281" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="P281" s="6" t="s">
-        <v>722</v>
+        <v>338</v>
       </c>
       <c r="Q281" s="2">
-        <v>63</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="282" spans="1:17">
       <c r="A282" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C282" s="6" t="s">
         <v>515</v>
@@ -14379,7 +14704,7 @@
         <v>40</v>
       </c>
       <c r="E282" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F282" s="2"/>
       <c r="G282" s="3">
@@ -14389,21 +14714,21 @@
         <v>1.5</v>
       </c>
       <c r="I282" s="2">
-        <v>72.3</v>
+        <v>50</v>
       </c>
       <c r="P282" s="6" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="Q282" s="2">
-        <v>91.35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="283" spans="1:17">
       <c r="A283" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C283" s="6" t="s">
         <v>515</v>
@@ -14412,7 +14737,7 @@
         <v>40</v>
       </c>
       <c r="E283" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F283" s="2"/>
       <c r="G283" s="3">
@@ -14425,7 +14750,7 @@
         <v>72.3</v>
       </c>
       <c r="P283" s="6" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="Q283" s="2">
         <v>91.35</v>
@@ -14433,10 +14758,10 @@
     </row>
     <row r="284" spans="1:17">
       <c r="A284" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C284" s="6" t="s">
         <v>515</v>
@@ -14445,11 +14770,9 @@
         <v>40</v>
       </c>
       <c r="E284" s="2">
-        <v>60</v>
-      </c>
-      <c r="F284" s="3" t="s">
-        <v>353</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F284" s="2"/>
       <c r="G284" s="3">
         <v>100</v>
       </c>
@@ -14457,13 +14780,13 @@
         <v>1.5</v>
       </c>
       <c r="I284" s="2">
-        <v>99</v>
+        <v>72.3</v>
       </c>
       <c r="P284" s="6" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="Q284" s="2">
-        <v>126</v>
+        <v>91.35</v>
       </c>
     </row>
     <row r="285" spans="1:17">
@@ -14483,7 +14806,7 @@
         <v>60</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G285" s="3">
         <v>100</v>
@@ -14503,7 +14826,7 @@
     </row>
     <row r="286" spans="1:17">
       <c r="A286" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B286" s="6" t="s">
         <v>305</v>
@@ -14517,62 +14840,64 @@
       <c r="E286" s="2">
         <v>60</v>
       </c>
-      <c r="F286" s="2"/>
+      <c r="F286" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="G286" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H286" s="3">
         <v>1.5</v>
       </c>
       <c r="I286" s="2">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="P286" s="6" t="s">
-        <v>339</v>
+        <v>725</v>
       </c>
       <c r="Q286" s="2">
-        <v>71.400000000000006</v>
+        <v>126</v>
       </c>
     </row>
     <row r="287" spans="1:17">
       <c r="A287" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B287" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D287" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E287" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F287" s="2"/>
       <c r="G287" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H287" s="3">
         <v>1.5</v>
       </c>
       <c r="I287" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="P287" s="6" t="s">
-        <v>726</v>
+        <v>339</v>
       </c>
       <c r="Q287" s="2">
-        <v>63</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="288" spans="1:17">
       <c r="A288" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B288" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C288" s="6" t="s">
         <v>516</v>
@@ -14581,7 +14906,7 @@
         <v>50</v>
       </c>
       <c r="E288" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F288" s="2"/>
       <c r="G288" s="3">
@@ -14591,21 +14916,21 @@
         <v>1.5</v>
       </c>
       <c r="I288" s="2">
-        <v>72.3</v>
+        <v>50</v>
       </c>
       <c r="P288" s="6" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="Q288" s="2">
-        <v>91.35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="289" spans="1:17">
       <c r="A289" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B289" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C289" s="6" t="s">
         <v>516</v>
@@ -14614,7 +14939,7 @@
         <v>50</v>
       </c>
       <c r="E289" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F289" s="2"/>
       <c r="G289" s="3">
@@ -14627,7 +14952,7 @@
         <v>72.3</v>
       </c>
       <c r="P289" s="6" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="Q289" s="2">
         <v>91.35</v>
@@ -14635,10 +14960,10 @@
     </row>
     <row r="290" spans="1:17">
       <c r="A290" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C290" s="6" t="s">
         <v>516</v>
@@ -14647,11 +14972,9 @@
         <v>50</v>
       </c>
       <c r="E290" s="2">
-        <v>60</v>
-      </c>
-      <c r="F290" s="3" t="s">
-        <v>353</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F290" s="2"/>
       <c r="G290" s="3">
         <v>100</v>
       </c>
@@ -14659,13 +14982,13 @@
         <v>1.5</v>
       </c>
       <c r="I290" s="2">
-        <v>99</v>
+        <v>72.3</v>
       </c>
       <c r="P290" s="6" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="Q290" s="2">
-        <v>126</v>
+        <v>91.35</v>
       </c>
     </row>
     <row r="291" spans="1:17">
@@ -14685,7 +15008,7 @@
         <v>60</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G291" s="3">
         <v>100</v>
@@ -14705,7 +15028,7 @@
     </row>
     <row r="292" spans="1:17">
       <c r="A292" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B292" s="6" t="s">
         <v>309</v>
@@ -14719,62 +15042,64 @@
       <c r="E292" s="2">
         <v>60</v>
       </c>
-      <c r="F292" s="2"/>
+      <c r="F292" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="G292" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H292" s="3">
         <v>1.5</v>
       </c>
       <c r="I292" s="2">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="P292" s="6" t="s">
-        <v>340</v>
+        <v>729</v>
       </c>
       <c r="Q292" s="2">
-        <v>71.400000000000006</v>
+        <v>126</v>
       </c>
     </row>
     <row r="293" spans="1:17">
       <c r="A293" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D293" s="2">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E293" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F293" s="2"/>
       <c r="G293" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H293" s="3">
         <v>1.5</v>
       </c>
       <c r="I293" s="2">
-        <v>72.349999999999994</v>
+        <v>59</v>
       </c>
       <c r="P293" s="6" t="s">
-        <v>730</v>
+        <v>340</v>
       </c>
       <c r="Q293" s="2">
-        <v>105</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="294" spans="1:17">
       <c r="A294" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B294" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C294" s="6" t="s">
         <v>517</v>
@@ -14783,7 +15108,7 @@
         <v>5</v>
       </c>
       <c r="E294" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F294" s="2"/>
       <c r="G294" s="3">
@@ -14793,21 +15118,21 @@
         <v>1.5</v>
       </c>
       <c r="I294" s="2">
-        <v>103</v>
+        <v>72.349999999999994</v>
       </c>
       <c r="P294" s="6" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="Q294" s="2">
-        <v>140.28</v>
+        <v>105</v>
       </c>
     </row>
     <row r="295" spans="1:17">
       <c r="A295" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C295" s="6" t="s">
         <v>517</v>
@@ -14816,7 +15141,7 @@
         <v>5</v>
       </c>
       <c r="E295" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F295" s="2"/>
       <c r="G295" s="3">
@@ -14829,7 +15154,7 @@
         <v>103</v>
       </c>
       <c r="P295" s="6" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="Q295" s="2">
         <v>140.28</v>
@@ -14837,10 +15162,10 @@
     </row>
     <row r="296" spans="1:17">
       <c r="A296" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C296" s="6" t="s">
         <v>517</v>
@@ -14849,11 +15174,9 @@
         <v>5</v>
       </c>
       <c r="E296" s="2">
-        <v>60</v>
-      </c>
-      <c r="F296" s="2" t="s">
-        <v>359</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F296" s="2"/>
       <c r="G296" s="3">
         <v>100</v>
       </c>
@@ -14861,13 +15184,13 @@
         <v>1.5</v>
       </c>
       <c r="I296" s="2">
-        <v>147.69999999999999</v>
+        <v>103</v>
       </c>
       <c r="P296" s="6" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="Q296" s="2">
-        <v>219.81</v>
+        <v>140.28</v>
       </c>
     </row>
     <row r="297" spans="1:17">
@@ -14886,8 +15209,8 @@
       <c r="E297" s="2">
         <v>60</v>
       </c>
-      <c r="F297" s="3" t="s">
-        <v>353</v>
+      <c r="F297" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="G297" s="3">
         <v>100</v>
@@ -14896,13 +15219,13 @@
         <v>1.5</v>
       </c>
       <c r="I297" s="2">
-        <v>143.69999999999999</v>
+        <v>147.69999999999999</v>
       </c>
       <c r="P297" s="6" t="s">
         <v>733</v>
       </c>
       <c r="Q297" s="2">
-        <v>210</v>
+        <v>219.81</v>
       </c>
     </row>
     <row r="298" spans="1:17">
@@ -14922,7 +15245,7 @@
         <v>60</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G298" s="3">
         <v>100</v>
@@ -14942,7 +15265,7 @@
     </row>
     <row r="299" spans="1:17">
       <c r="A299" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B299" s="6" t="s">
         <v>313</v>
@@ -14956,62 +15279,64 @@
       <c r="E299" s="2">
         <v>60</v>
       </c>
-      <c r="F299" s="2"/>
+      <c r="F299" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="G299" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H299" s="3">
         <v>1.5</v>
       </c>
       <c r="I299" s="2">
-        <v>81.349999999999994</v>
+        <v>143.69999999999999</v>
       </c>
       <c r="P299" s="6" t="s">
-        <v>341</v>
+        <v>733</v>
       </c>
       <c r="Q299" s="2">
-        <v>126</v>
+        <v>210</v>
       </c>
     </row>
     <row r="300" spans="1:17">
       <c r="A300" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B300" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D300" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E300" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F300" s="2"/>
       <c r="G300" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H300" s="3">
         <v>1.5</v>
       </c>
       <c r="I300" s="2">
-        <v>70.349999999999994</v>
+        <v>81.349999999999994</v>
       </c>
       <c r="P300" s="6" t="s">
-        <v>734</v>
+        <v>341</v>
       </c>
       <c r="Q300" s="2">
-        <v>105</v>
+        <v>126</v>
       </c>
     </row>
     <row r="301" spans="1:17">
       <c r="A301" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B301" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C301" s="6" t="s">
         <v>518</v>
@@ -15020,7 +15345,7 @@
         <v>15</v>
       </c>
       <c r="E301" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F301" s="2"/>
       <c r="G301" s="3">
@@ -15030,21 +15355,21 @@
         <v>1.5</v>
       </c>
       <c r="I301" s="2">
-        <v>101</v>
+        <v>70.349999999999994</v>
       </c>
       <c r="P301" s="6" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="Q301" s="2">
-        <v>140.28</v>
+        <v>105</v>
       </c>
     </row>
     <row r="302" spans="1:17">
       <c r="A302" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B302" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C302" s="6" t="s">
         <v>518</v>
@@ -15053,7 +15378,7 @@
         <v>15</v>
       </c>
       <c r="E302" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F302" s="2"/>
       <c r="G302" s="3">
@@ -15066,7 +15391,7 @@
         <v>101</v>
       </c>
       <c r="P302" s="6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="Q302" s="2">
         <v>140.28</v>
@@ -15074,10 +15399,10 @@
     </row>
     <row r="303" spans="1:17">
       <c r="A303" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B303" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C303" s="6" t="s">
         <v>518</v>
@@ -15086,11 +15411,9 @@
         <v>15</v>
       </c>
       <c r="E303" s="2">
-        <v>60</v>
-      </c>
-      <c r="F303" s="2" t="s">
-        <v>359</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F303" s="2"/>
       <c r="G303" s="3">
         <v>100</v>
       </c>
@@ -15098,13 +15421,13 @@
         <v>1.5</v>
       </c>
       <c r="I303" s="2">
-        <v>143.69999999999999</v>
+        <v>101</v>
       </c>
       <c r="P303" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="Q303" s="2">
-        <v>219.81</v>
+        <v>140.28</v>
       </c>
     </row>
     <row r="304" spans="1:17">
@@ -15123,8 +15446,8 @@
       <c r="E304" s="2">
         <v>60</v>
       </c>
-      <c r="F304" s="3" t="s">
-        <v>353</v>
+      <c r="F304" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="G304" s="3">
         <v>100</v>
@@ -15133,13 +15456,13 @@
         <v>1.5</v>
       </c>
       <c r="I304" s="2">
-        <v>139.69999999999999</v>
+        <v>143.69999999999999</v>
       </c>
       <c r="P304" s="6" t="s">
         <v>737</v>
       </c>
       <c r="Q304" s="2">
-        <v>210</v>
+        <v>219.81</v>
       </c>
     </row>
     <row r="305" spans="1:17">
@@ -15159,7 +15482,7 @@
         <v>60</v>
       </c>
       <c r="F305" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G305" s="3">
         <v>100</v>
@@ -15179,7 +15502,7 @@
     </row>
     <row r="306" spans="1:17">
       <c r="A306" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B306" s="6" t="s">
         <v>317</v>
@@ -15193,62 +15516,64 @@
       <c r="E306" s="2">
         <v>60</v>
       </c>
-      <c r="F306" s="2"/>
+      <c r="F306" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="G306" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H306" s="3">
         <v>1.5</v>
       </c>
       <c r="I306" s="2">
-        <v>79.349999999999994</v>
+        <v>139.69999999999999</v>
       </c>
       <c r="P306" s="6" t="s">
-        <v>342</v>
+        <v>737</v>
       </c>
       <c r="Q306" s="2">
-        <v>126</v>
+        <v>210</v>
       </c>
     </row>
     <row r="307" spans="1:17">
       <c r="A307" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B307" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D307" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E307" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F307" s="2"/>
       <c r="G307" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H307" s="3">
         <v>1.5</v>
       </c>
       <c r="I307" s="2">
-        <v>70.349999999999994</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="P307" s="6" t="s">
-        <v>738</v>
+        <v>342</v>
       </c>
       <c r="Q307" s="2">
-        <v>105</v>
+        <v>126</v>
       </c>
     </row>
     <row r="308" spans="1:17">
       <c r="A308" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B308" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C308" s="6" t="s">
         <v>519</v>
@@ -15257,7 +15582,7 @@
         <v>20</v>
       </c>
       <c r="E308" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F308" s="2"/>
       <c r="G308" s="3">
@@ -15267,21 +15592,21 @@
         <v>1.5</v>
       </c>
       <c r="I308" s="2">
-        <v>101</v>
+        <v>70.349999999999994</v>
       </c>
       <c r="P308" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="Q308" s="2">
-        <v>140.28</v>
+        <v>105</v>
       </c>
     </row>
     <row r="309" spans="1:17">
       <c r="A309" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B309" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C309" s="6" t="s">
         <v>519</v>
@@ -15290,7 +15615,7 @@
         <v>20</v>
       </c>
       <c r="E309" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F309" s="2"/>
       <c r="G309" s="3">
@@ -15303,7 +15628,7 @@
         <v>101</v>
       </c>
       <c r="P309" s="6" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="Q309" s="2">
         <v>140.28</v>
@@ -15311,10 +15636,10 @@
     </row>
     <row r="310" spans="1:17">
       <c r="A310" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B310" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C310" s="6" t="s">
         <v>519</v>
@@ -15323,11 +15648,9 @@
         <v>20</v>
       </c>
       <c r="E310" s="2">
-        <v>60</v>
-      </c>
-      <c r="F310" s="2" t="s">
-        <v>359</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F310" s="2"/>
       <c r="G310" s="3">
         <v>100</v>
       </c>
@@ -15335,13 +15658,13 @@
         <v>1.5</v>
       </c>
       <c r="I310" s="2">
-        <v>143.69999999999999</v>
+        <v>101</v>
       </c>
       <c r="P310" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="Q310" s="2">
-        <v>219.81</v>
+        <v>140.28</v>
       </c>
     </row>
     <row r="311" spans="1:17">
@@ -15360,8 +15683,8 @@
       <c r="E311" s="2">
         <v>60</v>
       </c>
-      <c r="F311" s="3" t="s">
-        <v>353</v>
+      <c r="F311" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="G311" s="3">
         <v>100</v>
@@ -15370,13 +15693,13 @@
         <v>1.5</v>
       </c>
       <c r="I311" s="2">
-        <v>139.69999999999999</v>
+        <v>143.69999999999999</v>
       </c>
       <c r="P311" s="6" t="s">
         <v>741</v>
       </c>
       <c r="Q311" s="2">
-        <v>210</v>
+        <v>219.81</v>
       </c>
     </row>
     <row r="312" spans="1:17">
@@ -15396,7 +15719,7 @@
         <v>60</v>
       </c>
       <c r="F312" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G312" s="3">
         <v>100</v>
@@ -15416,7 +15739,7 @@
     </row>
     <row r="313" spans="1:17">
       <c r="A313" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B313" s="6" t="s">
         <v>321</v>
@@ -15430,62 +15753,64 @@
       <c r="E313" s="2">
         <v>60</v>
       </c>
-      <c r="F313" s="2"/>
+      <c r="F313" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="G313" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H313" s="3">
         <v>1.5</v>
       </c>
       <c r="I313" s="2">
-        <v>79.349999999999994</v>
+        <v>139.69999999999999</v>
       </c>
       <c r="P313" s="6" t="s">
-        <v>343</v>
+        <v>741</v>
       </c>
       <c r="Q313" s="2">
-        <v>126</v>
+        <v>210</v>
       </c>
     </row>
     <row r="314" spans="1:17">
       <c r="A314" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B314" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D314" s="2">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E314" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F314" s="2"/>
       <c r="G314" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H314" s="3">
         <v>1.5</v>
       </c>
       <c r="I314" s="2">
-        <v>70.349999999999994</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="P314" s="6" t="s">
-        <v>742</v>
+        <v>343</v>
       </c>
       <c r="Q314" s="2">
-        <v>105</v>
+        <v>126</v>
       </c>
     </row>
     <row r="315" spans="1:17">
       <c r="A315" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B315" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C315" s="6" t="s">
         <v>520</v>
@@ -15494,7 +15819,7 @@
         <v>35</v>
       </c>
       <c r="E315" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F315" s="2"/>
       <c r="G315" s="3">
@@ -15504,21 +15829,21 @@
         <v>1.5</v>
       </c>
       <c r="I315" s="2">
-        <v>101</v>
+        <v>70.349999999999994</v>
       </c>
       <c r="P315" s="6" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="Q315" s="2">
-        <v>140.28</v>
+        <v>105</v>
       </c>
     </row>
     <row r="316" spans="1:17">
       <c r="A316" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B316" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C316" s="6" t="s">
         <v>520</v>
@@ -15527,7 +15852,7 @@
         <v>35</v>
       </c>
       <c r="E316" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F316" s="2"/>
       <c r="G316" s="3">
@@ -15540,7 +15865,7 @@
         <v>101</v>
       </c>
       <c r="P316" s="6" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="Q316" s="2">
         <v>140.28</v>
@@ -15548,10 +15873,10 @@
     </row>
     <row r="317" spans="1:17">
       <c r="A317" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B317" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C317" s="6" t="s">
         <v>520</v>
@@ -15560,11 +15885,9 @@
         <v>35</v>
       </c>
       <c r="E317" s="2">
-        <v>60</v>
-      </c>
-      <c r="F317" s="2" t="s">
-        <v>359</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F317" s="2"/>
       <c r="G317" s="3">
         <v>100</v>
       </c>
@@ -15572,13 +15895,13 @@
         <v>1.5</v>
       </c>
       <c r="I317" s="2">
-        <v>143.69999999999999</v>
+        <v>101</v>
       </c>
       <c r="P317" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="Q317" s="2">
-        <v>219.81</v>
+        <v>140.28</v>
       </c>
     </row>
     <row r="318" spans="1:17">
@@ -15597,8 +15920,8 @@
       <c r="E318" s="2">
         <v>60</v>
       </c>
-      <c r="F318" s="3" t="s">
-        <v>353</v>
+      <c r="F318" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="G318" s="3">
         <v>100</v>
@@ -15607,13 +15930,13 @@
         <v>1.5</v>
       </c>
       <c r="I318" s="2">
-        <v>139.69999999999999</v>
+        <v>143.69999999999999</v>
       </c>
       <c r="P318" s="6" t="s">
         <v>745</v>
       </c>
       <c r="Q318" s="2">
-        <v>210</v>
+        <v>219.81</v>
       </c>
     </row>
     <row r="319" spans="1:17">
@@ -15633,7 +15956,7 @@
         <v>60</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G319" s="3">
         <v>100</v>
@@ -15653,7 +15976,7 @@
     </row>
     <row r="320" spans="1:17">
       <c r="A320" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B320" s="6" t="s">
         <v>325</v>
@@ -15667,62 +15990,64 @@
       <c r="E320" s="2">
         <v>60</v>
       </c>
-      <c r="F320" s="2"/>
+      <c r="F320" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="G320" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H320" s="3">
         <v>1.5</v>
       </c>
       <c r="I320" s="2">
-        <v>79.349999999999994</v>
+        <v>139.69999999999999</v>
       </c>
       <c r="P320" s="6" t="s">
-        <v>344</v>
+        <v>745</v>
       </c>
       <c r="Q320" s="2">
-        <v>126</v>
+        <v>210</v>
       </c>
     </row>
     <row r="321" spans="1:17">
       <c r="A321" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D321" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E321" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F321" s="2"/>
       <c r="G321" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H321" s="3">
         <v>1.5</v>
       </c>
       <c r="I321" s="2">
-        <v>70.349999999999994</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="P321" s="6" t="s">
-        <v>746</v>
+        <v>344</v>
       </c>
       <c r="Q321" s="2">
-        <v>105</v>
+        <v>126</v>
       </c>
     </row>
     <row r="322" spans="1:17">
       <c r="A322" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B322" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C322" s="6" t="s">
         <v>521</v>
@@ -15731,7 +16056,7 @@
         <v>40</v>
       </c>
       <c r="E322" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F322" s="2"/>
       <c r="G322" s="3">
@@ -15741,21 +16066,21 @@
         <v>1.5</v>
       </c>
       <c r="I322" s="2">
-        <v>99</v>
+        <v>70.349999999999994</v>
       </c>
       <c r="P322" s="6" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="Q322" s="2">
-        <v>140.28</v>
+        <v>105</v>
       </c>
     </row>
     <row r="323" spans="1:17">
       <c r="A323" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B323" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C323" s="6" t="s">
         <v>521</v>
@@ -15764,7 +16089,7 @@
         <v>40</v>
       </c>
       <c r="E323" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F323" s="2"/>
       <c r="G323" s="3">
@@ -15777,7 +16102,7 @@
         <v>99</v>
       </c>
       <c r="P323" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q323" s="2">
         <v>140.28</v>
@@ -15785,10 +16110,10 @@
     </row>
     <row r="324" spans="1:17">
       <c r="A324" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B324" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C324" s="6" t="s">
         <v>521</v>
@@ -15797,11 +16122,9 @@
         <v>40</v>
       </c>
       <c r="E324" s="2">
-        <v>60</v>
-      </c>
-      <c r="F324" s="2" t="s">
-        <v>359</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F324" s="2"/>
       <c r="G324" s="3">
         <v>100</v>
       </c>
@@ -15809,13 +16132,13 @@
         <v>1.5</v>
       </c>
       <c r="I324" s="2">
-        <v>143.69999999999999</v>
+        <v>99</v>
       </c>
       <c r="P324" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="Q324" s="2">
-        <v>219.81</v>
+        <v>140.28</v>
       </c>
     </row>
     <row r="325" spans="1:17">
@@ -15834,8 +16157,8 @@
       <c r="E325" s="2">
         <v>60</v>
       </c>
-      <c r="F325" s="3" t="s">
-        <v>353</v>
+      <c r="F325" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="G325" s="3">
         <v>100</v>
@@ -15844,13 +16167,13 @@
         <v>1.5</v>
       </c>
       <c r="I325" s="2">
-        <v>139.69999999999999</v>
+        <v>143.69999999999999</v>
       </c>
       <c r="P325" s="6" t="s">
         <v>749</v>
       </c>
       <c r="Q325" s="2">
-        <v>210</v>
+        <v>219.81</v>
       </c>
     </row>
     <row r="326" spans="1:17">
@@ -15870,7 +16193,7 @@
         <v>60</v>
       </c>
       <c r="F326" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G326" s="3">
         <v>100</v>
@@ -15890,7 +16213,7 @@
     </row>
     <row r="327" spans="1:17">
       <c r="A327" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B327" s="6" t="s">
         <v>329</v>
@@ -15904,62 +16227,64 @@
       <c r="E327" s="2">
         <v>60</v>
       </c>
-      <c r="F327" s="2"/>
+      <c r="F327" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="G327" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H327" s="3">
         <v>1.5</v>
       </c>
       <c r="I327" s="2">
-        <v>79.349999999999994</v>
+        <v>139.69999999999999</v>
       </c>
       <c r="P327" s="6" t="s">
-        <v>345</v>
+        <v>749</v>
       </c>
       <c r="Q327" s="2">
-        <v>126</v>
+        <v>210</v>
       </c>
     </row>
     <row r="328" spans="1:17">
       <c r="A328" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B328" s="6" t="s">
-        <v>523</v>
+        <v>329</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="D328" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E328" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F328" s="2"/>
       <c r="G328" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H328" s="3">
         <v>1.5</v>
       </c>
       <c r="I328" s="2">
-        <v>73.8</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="P328" s="6" t="s">
-        <v>750</v>
+        <v>345</v>
       </c>
       <c r="Q328" s="2">
-        <v>105</v>
+        <v>126</v>
       </c>
     </row>
     <row r="329" spans="1:17">
       <c r="A329" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B329" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C329" s="6" t="s">
         <v>527</v>
@@ -15968,7 +16293,7 @@
         <v>50</v>
       </c>
       <c r="E329" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F329" s="2"/>
       <c r="G329" s="3">
@@ -15978,21 +16303,21 @@
         <v>1.5</v>
       </c>
       <c r="I329" s="2">
-        <v>103</v>
+        <v>73.8</v>
       </c>
       <c r="P329" s="6" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="Q329" s="2">
-        <v>140.28</v>
+        <v>105</v>
       </c>
     </row>
     <row r="330" spans="1:17">
       <c r="A330" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B330" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C330" s="6" t="s">
         <v>527</v>
@@ -16001,7 +16326,7 @@
         <v>50</v>
       </c>
       <c r="E330" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F330" s="2"/>
       <c r="G330" s="3">
@@ -16014,7 +16339,7 @@
         <v>103</v>
       </c>
       <c r="P330" s="6" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="Q330" s="2">
         <v>140.28</v>
@@ -16022,10 +16347,10 @@
     </row>
     <row r="331" spans="1:17">
       <c r="A331" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B331" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C331" s="6" t="s">
         <v>527</v>
@@ -16034,11 +16359,9 @@
         <v>50</v>
       </c>
       <c r="E331" s="2">
-        <v>60</v>
-      </c>
-      <c r="F331" s="2" t="s">
-        <v>359</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F331" s="2"/>
       <c r="G331" s="3">
         <v>100</v>
       </c>
@@ -16046,13 +16369,13 @@
         <v>1.5</v>
       </c>
       <c r="I331" s="2">
-        <v>150.6</v>
+        <v>103</v>
       </c>
       <c r="P331" s="6" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="Q331" s="2">
-        <v>219.81</v>
+        <v>140.28</v>
       </c>
     </row>
     <row r="332" spans="1:17">
@@ -16071,8 +16394,8 @@
       <c r="E332" s="2">
         <v>60</v>
       </c>
-      <c r="F332" s="3" t="s">
-        <v>353</v>
+      <c r="F332" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="G332" s="3">
         <v>100</v>
@@ -16081,13 +16404,13 @@
         <v>1.5</v>
       </c>
       <c r="I332" s="2">
-        <v>146.6</v>
+        <v>150.6</v>
       </c>
       <c r="P332" s="6" t="s">
         <v>753</v>
       </c>
       <c r="Q332" s="2">
-        <v>210</v>
+        <v>219.81</v>
       </c>
     </row>
     <row r="333" spans="1:17">
@@ -16107,7 +16430,7 @@
         <v>60</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G333" s="3">
         <v>100</v>
@@ -16127,7 +16450,7 @@
     </row>
     <row r="334" spans="1:17">
       <c r="A334" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B334" s="6" t="s">
         <v>526</v>
@@ -16141,62 +16464,64 @@
       <c r="E334" s="2">
         <v>60</v>
       </c>
-      <c r="F334" s="2"/>
+      <c r="F334" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="G334" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H334" s="3">
         <v>1.5</v>
       </c>
       <c r="I334" s="2">
-        <v>82.8</v>
+        <v>146.6</v>
       </c>
       <c r="P334" s="6" t="s">
-        <v>346</v>
+        <v>753</v>
       </c>
       <c r="Q334" s="2">
-        <v>126</v>
+        <v>210</v>
       </c>
     </row>
     <row r="335" spans="1:17">
       <c r="A335" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>330</v>
+        <v>526</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="D335" s="2">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E335" s="2">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F335" s="2"/>
       <c r="G335" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H335" s="3">
         <v>1.5</v>
       </c>
       <c r="I335" s="2">
-        <v>85.2</v>
+        <v>82.8</v>
       </c>
       <c r="P335" s="6" t="s">
-        <v>754</v>
+        <v>346</v>
       </c>
       <c r="Q335" s="2">
-        <v>117.08</v>
+        <v>126</v>
       </c>
     </row>
     <row r="336" spans="1:17">
       <c r="A336" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C336" s="6" t="s">
         <v>522</v>
@@ -16205,7 +16530,7 @@
         <v>70</v>
       </c>
       <c r="E336" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F336" s="2"/>
       <c r="G336" s="3">
@@ -16215,21 +16540,21 @@
         <v>1.5</v>
       </c>
       <c r="I336" s="2">
-        <v>120.8</v>
+        <v>85.2</v>
       </c>
       <c r="P336" s="6" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="Q336" s="2">
-        <v>156.03</v>
+        <v>117.08</v>
       </c>
     </row>
     <row r="337" spans="1:19">
       <c r="A337" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C337" s="6" t="s">
         <v>522</v>
@@ -16238,7 +16563,7 @@
         <v>70</v>
       </c>
       <c r="E337" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F337" s="2"/>
       <c r="G337" s="3">
@@ -16251,7 +16576,7 @@
         <v>120.8</v>
       </c>
       <c r="P337" s="6" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="Q337" s="2">
         <v>156.03</v>
@@ -16259,10 +16584,10 @@
     </row>
     <row r="338" spans="1:19">
       <c r="A338" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C338" s="6" t="s">
         <v>522</v>
@@ -16271,11 +16596,9 @@
         <v>70</v>
       </c>
       <c r="E338" s="2">
-        <v>60</v>
-      </c>
-      <c r="F338" s="2" t="s">
-        <v>359</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F338" s="2"/>
       <c r="G338" s="3">
         <v>100</v>
       </c>
@@ -16283,15 +16606,14 @@
         <v>1.5</v>
       </c>
       <c r="I338" s="2">
-        <v>173.4</v>
+        <v>120.8</v>
       </c>
       <c r="P338" s="6" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="Q338" s="2">
-        <v>243.96</v>
-      </c>
-      <c r="R338" s="2"/>
+        <v>156.03</v>
+      </c>
     </row>
     <row r="339" spans="1:19">
       <c r="A339" s="5" t="s">
@@ -16309,8 +16631,8 @@
       <c r="E339" s="2">
         <v>60</v>
       </c>
-      <c r="F339" s="3" t="s">
-        <v>353</v>
+      <c r="F339" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="G339" s="3">
         <v>100</v>
@@ -16319,14 +16641,15 @@
         <v>1.5</v>
       </c>
       <c r="I339" s="2">
-        <v>169.4</v>
+        <v>173.4</v>
       </c>
       <c r="P339" s="6" t="s">
         <v>757</v>
       </c>
       <c r="Q339" s="2">
-        <v>234.15</v>
-      </c>
+        <v>243.96</v>
+      </c>
+      <c r="R339" s="2"/>
     </row>
     <row r="340" spans="1:19">
       <c r="A340" s="5" t="s">
@@ -16345,7 +16668,7 @@
         <v>60</v>
       </c>
       <c r="F340" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G340" s="3">
         <v>100</v>
@@ -16365,7 +16688,7 @@
     </row>
     <row r="341" spans="1:19">
       <c r="A341" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B341" s="6" t="s">
         <v>333</v>
@@ -16379,70 +16702,70 @@
       <c r="E341" s="2">
         <v>60</v>
       </c>
-      <c r="F341" s="2"/>
+      <c r="F341" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="G341" s="3">
+        <v>100</v>
+      </c>
+      <c r="H341" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="I341" s="2">
+        <v>169.4</v>
+      </c>
+      <c r="P341" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="Q341" s="2">
+        <v>234.15</v>
+      </c>
+    </row>
+    <row r="342" spans="1:19">
+      <c r="A342" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B342" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="C342" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="D342" s="2">
+        <v>70</v>
+      </c>
+      <c r="E342" s="2">
+        <v>60</v>
+      </c>
+      <c r="F342" s="2"/>
+      <c r="G342" s="3">
         <v>50</v>
       </c>
-      <c r="H341" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="I341" s="2">
+      <c r="H342" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="I342" s="2">
         <v>94.2</v>
       </c>
-      <c r="P341" s="6" t="s">
+      <c r="P342" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="Q341" s="2">
+      <c r="Q342" s="2">
         <v>140.49</v>
       </c>
     </row>
-    <row r="342" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A342" s="5" t="s">
+    <row r="343" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A343" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="B342" s="8" t="s">
+      <c r="B343" s="8" t="s">
         <v>662</v>
-      </c>
-      <c r="D342" s="3">
-        <v>15</v>
-      </c>
-      <c r="E342" s="3">
-        <v>60</v>
-      </c>
-      <c r="G342" s="3">
-        <v>100</v>
-      </c>
-      <c r="H342" s="3">
-        <v>2</v>
-      </c>
-      <c r="I342" s="3">
-        <v>144</v>
-      </c>
-      <c r="L342" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="M342" s="3">
-        <v>288.60550458715596</v>
-      </c>
-      <c r="R342" s="5" t="s">
-        <v>664</v>
-      </c>
-      <c r="S342">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="343" spans="1:19">
-      <c r="A343" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="B343" s="8" t="s">
-        <v>663</v>
       </c>
       <c r="D343" s="3">
         <v>15</v>
       </c>
       <c r="E343" s="3">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G343" s="3">
         <v>100</v>
@@ -16451,33 +16774,33 @@
         <v>2</v>
       </c>
       <c r="I343" s="3">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="L343" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="M343" s="3">
+        <v>288.60550458715596</v>
+      </c>
+      <c r="R343" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="S343">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="344" spans="1:19">
+      <c r="A344" s="5" t="s">
         <v>661</v>
       </c>
-      <c r="M343" s="3">
-        <v>346.32660550458712</v>
-      </c>
-      <c r="R343" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="S343">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="344" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A344" s="5" t="s">
-        <v>666</v>
-      </c>
       <c r="B344" s="8" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="D344" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E344" s="3">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G344" s="3">
         <v>100</v>
@@ -16486,33 +16809,33 @@
         <v>2</v>
       </c>
       <c r="I344" s="3">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="L344" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="M344" s="3">
+        <v>346.32660550458712</v>
+      </c>
+      <c r="R344" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="S344">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="345" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A345" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="M344" s="3">
-        <v>288.60550458715596</v>
-      </c>
-      <c r="R344" s="5" t="s">
-        <v>668</v>
-      </c>
-      <c r="S344">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="345" spans="1:19">
-      <c r="A345" s="5" t="s">
-        <v>669</v>
-      </c>
       <c r="B345" s="8" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D345" s="3">
         <v>25</v>
       </c>
       <c r="E345" s="3">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G345" s="3">
         <v>100</v>
@@ -16521,33 +16844,33 @@
         <v>2</v>
       </c>
       <c r="I345" s="3">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="L345" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="M345" s="3">
+        <v>288.60550458715596</v>
+      </c>
+      <c r="R345" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="S345">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="346" spans="1:19">
+      <c r="A346" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="M345" s="3">
-        <v>346.32660550458712</v>
-      </c>
-      <c r="R345" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="S345">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="346" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A346" s="5" t="s">
-        <v>678</v>
-      </c>
       <c r="B346" s="8" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="D346" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E346" s="3">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G346" s="3">
         <v>100</v>
@@ -16556,33 +16879,33 @@
         <v>2</v>
       </c>
       <c r="I346" s="3">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="L346" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="M346" s="3">
+        <v>346.32660550458712</v>
+      </c>
+      <c r="R346" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="S346">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="347" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A347" s="5" t="s">
         <v>678</v>
       </c>
-      <c r="M346" s="3">
-        <v>257.68</v>
-      </c>
-      <c r="R346" s="5" t="s">
-        <v>680</v>
-      </c>
-      <c r="S346">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="347" spans="1:19">
-      <c r="A347" s="5" t="s">
-        <v>681</v>
-      </c>
       <c r="B347" s="8" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D347" s="3">
         <v>5</v>
       </c>
       <c r="E347" s="3">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G347" s="3">
         <v>100</v>
@@ -16591,33 +16914,33 @@
         <v>2</v>
       </c>
       <c r="I347" s="3">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="L347" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="M347" s="3">
+        <v>257.68</v>
+      </c>
+      <c r="R347" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="S347">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="348" spans="1:19">
+      <c r="A348" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="M347" s="3">
-        <v>309.22000000000003</v>
-      </c>
-      <c r="R347" s="5" t="s">
-        <v>683</v>
-      </c>
-      <c r="S347">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="348" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A348" s="5" t="s">
-        <v>674</v>
-      </c>
       <c r="B348" s="8" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D348" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E348" s="3">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G348" s="3">
         <v>100</v>
@@ -16626,33 +16949,33 @@
         <v>2</v>
       </c>
       <c r="I348" s="3">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="L348" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="M348" s="3">
+        <v>309.22000000000003</v>
+      </c>
+      <c r="R348" s="5" t="s">
+        <v>683</v>
+      </c>
+      <c r="S348">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="349" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A349" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="M348" s="3">
-        <v>257.68</v>
-      </c>
-      <c r="R348" s="5" t="s">
-        <v>675</v>
-      </c>
-      <c r="S348">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="349" spans="1:19">
-      <c r="A349" s="5" t="s">
-        <v>676</v>
-      </c>
       <c r="B349" s="8" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D349" s="3">
         <v>15</v>
       </c>
       <c r="E349" s="3">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G349" s="3">
         <v>100</v>
@@ -16661,33 +16984,33 @@
         <v>2</v>
       </c>
       <c r="I349" s="3">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="L349" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="M349" s="3">
+        <v>257.68</v>
+      </c>
+      <c r="R349" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="S349">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="350" spans="1:19">
+      <c r="A350" s="5" t="s">
         <v>676</v>
       </c>
-      <c r="M349" s="3">
-        <v>309.22000000000003</v>
-      </c>
-      <c r="R349" s="5" t="s">
-        <v>677</v>
-      </c>
-      <c r="S349">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="350" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A350" s="5" t="s">
-        <v>684</v>
-      </c>
       <c r="B350" s="8" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="D350" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E350" s="3">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G350" s="3">
         <v>100</v>
@@ -16696,33 +17019,33 @@
         <v>2</v>
       </c>
       <c r="I350" s="3">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="L350" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="M350" s="3">
+        <v>309.22000000000003</v>
+      </c>
+      <c r="R350" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="S350">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="351" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A351" s="5" t="s">
         <v>684</v>
       </c>
-      <c r="M350" s="3">
-        <v>257.68</v>
-      </c>
-      <c r="R350" s="5" t="s">
-        <v>686</v>
-      </c>
-      <c r="S350">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="351" spans="1:19">
-      <c r="A351" s="5" t="s">
-        <v>687</v>
-      </c>
       <c r="B351" s="8" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D351" s="3">
         <v>25</v>
       </c>
       <c r="E351" s="3">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G351" s="3">
         <v>100</v>
@@ -16731,33 +17054,33 @@
         <v>2</v>
       </c>
       <c r="I351" s="3">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="L351" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="M351" s="3">
+        <v>257.68</v>
+      </c>
+      <c r="R351" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="S351">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="352" spans="1:19">
+      <c r="A352" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="M351" s="3">
-        <v>309.22000000000003</v>
-      </c>
-      <c r="R351" s="5" t="s">
-        <v>689</v>
-      </c>
-      <c r="S351">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="352" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A352" s="5" t="s">
-        <v>690</v>
-      </c>
       <c r="B352" s="8" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D352" s="3">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E352" s="3">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G352" s="3">
         <v>100</v>
@@ -16766,33 +17089,33 @@
         <v>2</v>
       </c>
       <c r="I352" s="3">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="L352" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="M352" s="3">
+        <v>309.22000000000003</v>
+      </c>
+      <c r="R352" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="S352">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="353" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A353" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="M352" s="3">
-        <v>257.68</v>
-      </c>
-      <c r="R352" s="5" t="s">
-        <v>692</v>
-      </c>
-      <c r="S352">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="353" spans="1:19">
-      <c r="A353" s="5" t="s">
-        <v>693</v>
-      </c>
       <c r="B353" s="8" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D353" s="3">
         <v>35</v>
       </c>
       <c r="E353" s="3">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G353" s="3">
         <v>100</v>
@@ -16801,29 +17124,65 @@
         <v>2</v>
       </c>
       <c r="I353" s="3">
+        <v>144</v>
+      </c>
+      <c r="L353" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="M353" s="3">
+        <v>257.68</v>
+      </c>
+      <c r="R353" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="S353">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="354" spans="1:19">
+      <c r="A354" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="B354" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="D354" s="3">
+        <v>35</v>
+      </c>
+      <c r="E354" s="3">
+        <v>72</v>
+      </c>
+      <c r="G354" s="3">
+        <v>100</v>
+      </c>
+      <c r="H354" s="3">
+        <v>2</v>
+      </c>
+      <c r="I354" s="3">
         <v>170</v>
       </c>
-      <c r="L353" s="5" t="s">
+      <c r="L354" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="M353" s="3">
+      <c r="M354" s="3">
         <v>309.22000000000003</v>
       </c>
-      <c r="R353" s="5" t="s">
+      <c r="R354" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="S353">
+      <c r="S354">
         <v>170</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="G1:G2"/>
